--- a/AAII_Financials/Quarterly/BTBT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BTBT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/BTBT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BTBT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
   <si>
     <t>BTBT</t>
   </si>
@@ -656,243 +656,256 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43465</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43281</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43100</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42916</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42825</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>16100</v>
+      </c>
+      <c r="F8" s="3">
         <v>11600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>9000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>8300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>7800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>9100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>6800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>8600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>13400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>10400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>28300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>44000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>20400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>7900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>700</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
         <v>4500</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
         <v>4900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>4200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>9900</v>
+      </c>
+      <c r="F9" s="3">
         <v>8800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>5700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>5200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>6000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>6500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>3600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>4300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>4800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>2600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>10900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>12500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>13400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>6200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>700</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S9" s="3">
-        <v>0</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>4</v>
+      <c r="U9" s="3">
+        <v>0</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>4</v>
@@ -906,65 +919,71 @@
       <c r="Y9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F10" s="3">
         <v>2800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>3300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>3100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>1800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>2600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>3200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>4300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>8600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>7800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>17400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>31500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>7000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1700</v>
       </c>
-      <c r="Q10" s="3">
-        <v>0</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S10" s="3">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U10" s="3">
         <v>4500</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>4</v>
       </c>
@@ -977,8 +996,14 @@
       <c r="Y10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1004,8 +1029,10 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1054,29 +1081,35 @@
       <c r="R12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S12" s="3">
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U12" s="3">
         <v>400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1146,47 +1179,53 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-45700</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F14" s="3">
         <v>2100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>1400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>2200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>48600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>2700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>27000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>14700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>18900</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>9000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1199,11 +1238,11 @@
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1217,79 +1256,91 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>3600</v>
+        <v>6800</v>
       </c>
       <c r="E15" s="3">
-        <v>3700</v>
+        <v>3400</v>
       </c>
       <c r="F15" s="3">
         <v>3600</v>
       </c>
       <c r="G15" s="3">
+        <v>3700</v>
+      </c>
+      <c r="H15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I15" s="3">
         <v>9400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>9300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>5300</v>
-      </c>
-      <c r="J15" s="3">
-        <v>3800</v>
-      </c>
-      <c r="K15" s="3">
-        <v>3300</v>
       </c>
       <c r="L15" s="3">
         <v>3800</v>
       </c>
       <c r="M15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N15" s="3">
+        <v>3800</v>
+      </c>
+      <c r="O15" s="3">
         <v>2300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>3700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>3300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>1200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>100</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T15" s="3">
         <v>0</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>4</v>
+      <c r="V15" s="3">
+        <v>0</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1312,150 +1363,164 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>20000</v>
+      </c>
+      <c r="F17" s="3">
         <v>18600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>11700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>11300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>70300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>23500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>24700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>14900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>19300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>26000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>26600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>18300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>18900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>7800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>9800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>5700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>4700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-7000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-2700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-3000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-62500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-14400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-17900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-6300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-5900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-15600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>25700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-2000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-5300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-1900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1481,150 +1546,164 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-6900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-3700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-2900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>10400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>800</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-1200</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-3500</v>
+        <v>58500</v>
       </c>
       <c r="E21" s="3">
         <v>1400</v>
       </c>
       <c r="F21" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="G21" s="3">
         <v>1400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I21" s="3">
         <v>-53900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-5000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-11300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-9500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-15400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>39700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>5500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>1300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-2000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-6400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-1800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-700</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-400</v>
-      </c>
-      <c r="W21" s="3">
-        <v>-400</v>
       </c>
       <c r="X21" s="3">
         <v>-400</v>
       </c>
       <c r="Y21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1694,150 +1773,168 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-7100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-2300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-2200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-63300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-14300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-16600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-5700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-12800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-19200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>36100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>2300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-2000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-6500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-1900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="E24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3">
         <v>100</v>
       </c>
       <c r="G24" s="3">
+        <v>100</v>
+      </c>
+      <c r="H24" s="3">
+        <v>100</v>
+      </c>
+      <c r="I24" s="3">
         <v>-600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>1200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-1400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>2500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>4</v>
+      <c r="S24" s="3">
+        <v>0</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
-      <c r="U24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>100</v>
-      </c>
-      <c r="V24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="W24" s="3">
-        <v>-100</v>
       </c>
       <c r="X24" s="3">
         <v>-100</v>
       </c>
       <c r="Y24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1907,150 +2004,168 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-7200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-2400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-2300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-62700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-14500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-17800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-4300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-15300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-20100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>35800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>2300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-2000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-6500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-1900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-7200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-2400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-2300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-62700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-14500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-17800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-4300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-15300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-20100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>35800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>2300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-400</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-6500</v>
       </c>
       <c r="T27" s="3">
         <v>-1800</v>
       </c>
       <c r="U27" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="V27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="W27" s="3">
         <v>-700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2120,37 +2235,43 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>4</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2159,40 +2280,46 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>-100</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>-3700</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>-7700</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V29" s="3">
         <v>-1600</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="X29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2262,8 +2389,14 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2333,150 +2466,168 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>6900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>3700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>2900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-10400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-800</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>1200</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-7200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-2400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-2300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-62700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-14500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-17800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-4300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-15300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-20100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>35800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>2200</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>-4100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-9500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-6500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-3400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2546,155 +2697,173 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-7200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-2400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-2300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-62700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-14500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-17800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-4300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-15300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-20100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>35800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>2200</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>-4100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-9500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-6500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-3400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43465</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43281</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43100</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42916</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42825</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2720,8 +2889,10 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2747,130 +2918,138 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>16900</v>
+      </c>
+      <c r="F41" s="3">
         <v>20800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>18500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>27900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>32700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>32300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>44300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>28100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>42400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>26500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>28300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2500</v>
       </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3">
         <v>400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>2300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>10000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>5500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>5600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>6200</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>138200</v>
+      </c>
+      <c r="E42" s="3">
+        <v>47700</v>
+      </c>
+      <c r="F42" s="3">
         <v>40200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>31600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>27100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>27600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>23300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>26900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>43900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>29000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>35000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>21000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>29400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>6200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>200</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2883,41 +3062,47 @@
       <c r="W42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="X42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>700</v>
+        <v>10200</v>
       </c>
       <c r="E43" s="3">
-        <v>700</v>
+        <v>13900</v>
       </c>
       <c r="F43" s="3">
         <v>700</v>
       </c>
       <c r="G43" s="3">
+        <v>700</v>
+      </c>
+      <c r="H43" s="3">
+        <v>700</v>
+      </c>
+      <c r="I43" s="3">
         <v>800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>200</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2930,38 +3115,44 @@
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T43" s="3">
         <v>500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>700</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3031,179 +3222,197 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F45" s="3">
         <v>4800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>5200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>3000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>3400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>12700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>7000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>6300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>18900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>3100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>10400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>4900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>2100</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
       <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>3200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>4300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>3900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>700</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>189500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>83300</v>
+      </c>
+      <c r="F46" s="3">
         <v>66500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>56000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>58700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>64400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>68400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>78400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>78300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>90300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>64600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>59600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>34500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>8700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>3000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>5700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>12100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>10100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>9600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>7600</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F47" s="3">
         <v>4400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>5400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>4300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>2400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>300</v>
-      </c>
-      <c r="K47" s="3">
-        <v>1000</v>
-      </c>
-      <c r="L47" s="3">
-        <v>1000</v>
       </c>
       <c r="M47" s="3">
         <v>1000</v>
@@ -3211,11 +3420,11 @@
       <c r="N47" s="3">
         <v>1000</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>4</v>
+      <c r="O47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P47" s="3">
+        <v>1000</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>4</v>
@@ -3229,11 +3438,11 @@
       <c r="T47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
-      </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -3244,67 +3453,73 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>87700</v>
+      </c>
+      <c r="F48" s="3">
         <v>25100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>24500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>19000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>22600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>80700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>90000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>28700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>71600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>30000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>36000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>28200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>29800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>17700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>4400</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
-      </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+      <c r="U48" s="3">
         <v>700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>700</v>
-      </c>
-      <c r="U48" s="3">
-        <v>100</v>
-      </c>
-      <c r="V48" s="3">
-        <v>100</v>
       </c>
       <c r="W48" s="3">
         <v>100</v>
@@ -3312,11 +3527,17 @@
       <c r="X48" s="3">
         <v>100</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3386,8 +3607,14 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3457,8 +3684,14 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3528,79 +3761,91 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>13500</v>
+      </c>
+      <c r="F52" s="3">
         <v>12800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>14400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>10200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>11600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>13300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>10200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>62300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>49900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>14800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>11500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>14400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1300</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S52" s="3">
         <v>6900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>4000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>5400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>6100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>3100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>2800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>3300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1300</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3670,79 +3915,91 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>291100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>189300</v>
+      </c>
+      <c r="F54" s="3">
         <v>108700</v>
-      </c>
-      <c r="E54" s="3">
-        <v>100400</v>
-      </c>
-      <c r="F54" s="3">
-        <v>92200</v>
       </c>
       <c r="G54" s="3">
         <v>100400</v>
       </c>
       <c r="H54" s="3">
+        <v>92200</v>
+      </c>
+      <c r="I54" s="3">
+        <v>100400</v>
+      </c>
+      <c r="J54" s="3">
         <v>164700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>179000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>169600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>173700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>110400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>108100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>78100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>39900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>20600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>14000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>4500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>7500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>12500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>15300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>12900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>13000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>9000</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3768,8 +4025,10 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3795,59 +4054,61 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F57" s="3">
         <v>1100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>3500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>100</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3857,17 +4118,23 @@
       <c r="V57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
-      </c>
-      <c r="X57" s="3">
-        <v>0</v>
+      <c r="W57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3895,21 +4162,21 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P58" s="3">
         <v>1300</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3922,11 +4189,11 @@
       <c r="T58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -3937,150 +4204,168 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>24800</v>
+      </c>
+      <c r="F59" s="3">
         <v>1100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>4000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>3800</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I59" s="3">
-        <v>2200</v>
       </c>
       <c r="J59" s="3">
         <v>1300</v>
       </c>
       <c r="K59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M59" s="3">
         <v>2400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1100</v>
-      </c>
-      <c r="R59" s="3">
-        <v>400</v>
-      </c>
-      <c r="S59" s="3">
-        <v>2400</v>
       </c>
       <c r="T59" s="3">
         <v>400</v>
       </c>
       <c r="U59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="V59" s="3">
         <v>400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
+        <v>400</v>
+      </c>
+      <c r="X59" s="3">
         <v>500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>400</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>27100</v>
+      </c>
+      <c r="F60" s="3">
         <v>2200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>4100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>5000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>3200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1200</v>
-      </c>
-      <c r="R60" s="3">
-        <v>400</v>
-      </c>
-      <c r="S60" s="3">
-        <v>2400</v>
       </c>
       <c r="T60" s="3">
         <v>400</v>
       </c>
       <c r="U60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="V60" s="3">
         <v>400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
+        <v>400</v>
+      </c>
+      <c r="X60" s="3">
         <v>500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>400</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4150,49 +4435,55 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>9500</v>
+      </c>
+      <c r="F62" s="3">
         <v>3200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>3200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>3100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>3000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>3000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>2900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>2800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>3200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>700</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>4</v>
@@ -4206,11 +4497,11 @@
       <c r="T62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
-      </c>
-      <c r="V62" s="3">
-        <v>0</v>
+      <c r="U62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
@@ -4221,8 +4512,14 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4292,8 +4589,14 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4363,8 +4666,14 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4434,79 +4743,91 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>36600</v>
+      </c>
+      <c r="F66" s="3">
         <v>5400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>8600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>5200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>10500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>6400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>7000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>7700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>8300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>4400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>2400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1300</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4532,8 +4853,10 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4603,8 +4926,14 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4674,8 +5003,14 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4707,10 +5042,10 @@
         <v>9100</v>
       </c>
       <c r="M70" s="3">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="N70" s="3">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="O70" s="3">
         <v>0</v>
@@ -4745,8 +5080,14 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4816,79 +5157,91 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-75600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-146900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-144100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-136900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-134500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-131400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-62500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-48200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-30100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-26100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-10400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>18700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>20100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-15700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-18400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-17900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-13800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-10800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-4300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-1600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-200</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4958,8 +5311,14 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5029,8 +5388,14 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5100,79 +5465,91 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>256100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>143700</v>
+      </c>
+      <c r="F76" s="3">
         <v>94200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>82700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>77900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>80900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>149200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>162900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>152800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>156400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>97000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>104800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>75000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>38000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>19900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>12500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>3800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>5200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>11600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>14300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>11800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>11600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>7700</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5242,155 +5619,173 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43465</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43281</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43100</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42916</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42825</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-7200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-2400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-2300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-62700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-14500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-17800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-4300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-15300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-20100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>35800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>2200</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>-4100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-9500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-6500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-3400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5416,67 +5811,69 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3600</v>
+        <v>6800</v>
       </c>
       <c r="E83" s="3">
-        <v>3700</v>
+        <v>3400</v>
       </c>
       <c r="F83" s="3">
         <v>3600</v>
       </c>
       <c r="G83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="H83" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I83" s="3">
         <v>9400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>9300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>5300</v>
-      </c>
-      <c r="J83" s="3">
-        <v>3800</v>
-      </c>
-      <c r="K83" s="3">
-        <v>3300</v>
       </c>
       <c r="L83" s="3">
         <v>3800</v>
       </c>
       <c r="M83" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N83" s="3">
+        <v>3800</v>
+      </c>
+      <c r="O83" s="3">
         <v>2300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>3700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>3300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>100</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
       </c>
       <c r="S83" s="3">
         <v>100</v>
       </c>
       <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3">
         <v>100</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
       <c r="V83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -5487,8 +5884,14 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5558,8 +5961,14 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5629,8 +6038,14 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5700,8 +6115,14 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5771,8 +6192,14 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5842,79 +6269,91 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>24300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-13900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-7800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-9000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-9700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-2300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-2500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-1300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-2000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-5100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-500</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5940,68 +6379,70 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-58400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-7100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-8300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-11100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-46000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>6700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-11200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V91" s="3">
         <v>-800</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
@@ -6009,10 +6450,16 @@
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6082,8 +6529,14 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6153,68 +6606,74 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-58400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-8200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-2500</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-18300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>3800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-4100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-43700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>1800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>1100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>8600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-10700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-900</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V94" s="3">
         <v>-3300</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
@@ -6222,10 +6681,16 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6251,8 +6716,10 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6322,8 +6789,14 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6393,8 +6866,14 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6464,8 +6943,14 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6535,79 +7020,91 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>30100</v>
+      </c>
+      <c r="F100" s="3">
         <v>16300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>6700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>21000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-2200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>71700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>4700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>28500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>1300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-8300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>6500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>13500</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V100" s="3">
         <v>5900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>5700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-400</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6660,92 +7157,104 @@
         <v>0</v>
       </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F102" s="3">
         <v>2300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-9400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-4800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-12000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>16200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-13000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>15900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>28000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-2100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>1900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-2300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-2500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>5100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>6700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BTBT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BTBT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>BTBT</t>
   </si>
@@ -656,259 +656,266 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>42825</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E8" s="3">
         <v>30300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>16100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>28300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>44000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>20400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>700</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
       <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
         <v>4500</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
-      </c>
       <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
         <v>4900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4200</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>1400</v>
       </c>
       <c r="Z8" s="3">
         <v>1400</v>
       </c>
       <c r="AA8" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AB8" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E9" s="3">
         <v>16200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>700</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U9" s="3">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>4</v>
+      <c r="U9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V9" s="3">
+        <v>0</v>
       </c>
       <c r="W9" s="3" t="s">
         <v>4</v>
@@ -925,68 +932,71 @@
       <c r="AA9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E10" s="3">
         <v>14100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>7800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>17400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>31500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>7000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1700</v>
       </c>
-      <c r="S10" s="3">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="T10" s="3">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V10" s="3">
         <v>4500</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1002,8 +1012,11 @@
       <c r="AA10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1031,8 +1044,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1087,29 +1101,32 @@
       <c r="T12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U12" s="3">
+      <c r="U12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V12" s="3">
         <v>400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>200</v>
-      </c>
-      <c r="W12" s="3">
-        <v>300</v>
       </c>
       <c r="X12" s="3">
         <v>300</v>
       </c>
       <c r="Y12" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Z12" s="3">
         <v>100</v>
       </c>
       <c r="AA12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB12" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1185,50 +1202,53 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-45700</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>2900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>48600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>27000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>14700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>18900</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>9000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1244,8 +1264,8 @@
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1262,70 +1282,73 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E15" s="3">
         <v>6800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>9400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>9300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>100</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V15" s="3">
-        <v>0</v>
-      </c>
-      <c r="W15" s="3" t="s">
-        <v>4</v>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>4</v>
@@ -1333,14 +1356,17 @@
       <c r="Y15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z15" s="3">
-        <v>0</v>
+      <c r="Z15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1365,162 +1391,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E17" s="3">
         <v>-16800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>20000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>70300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>24700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>19300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>26000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>26600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4700</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>1800</v>
       </c>
       <c r="Z17" s="3">
         <v>1800</v>
       </c>
       <c r="AA17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AB17" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E18" s="3">
         <v>47100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-62500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-14400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-17900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-15600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>25700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-500</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-400</v>
       </c>
       <c r="Z18" s="3">
         <v>-400</v>
       </c>
       <c r="AA18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AB18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1548,56 +1581,57 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>4600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-6900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>10400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>800</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1605,17 +1639,17 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-1200</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
@@ -1625,73 +1659,76 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E21" s="3">
         <v>58500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3500</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1400</v>
       </c>
       <c r="H21" s="3">
         <v>1400</v>
       </c>
       <c r="I21" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J21" s="3">
         <v>-53900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-5000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-11300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-9500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-15400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>39700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-6400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-700</v>
-      </c>
-      <c r="X21" s="3">
-        <v>-400</v>
       </c>
       <c r="Y21" s="3">
         <v>-400</v>
@@ -1700,10 +1737,13 @@
         <v>-400</v>
       </c>
       <c r="AA21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AB21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1779,96 +1819,102 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E23" s="3">
         <v>51700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-63300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-16600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-12800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-19200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>36100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-500</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-400</v>
       </c>
       <c r="Z23" s="3">
         <v>-400</v>
       </c>
       <c r="AA23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AB23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>500</v>
+      </c>
+      <c r="E24" s="3">
         <v>1600</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3">
         <v>100</v>
@@ -1877,32 +1923,32 @@
         <v>100</v>
       </c>
       <c r="I24" s="3">
+        <v>100</v>
+      </c>
+      <c r="J24" s="3">
         <v>-600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -1912,17 +1958,17 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>100</v>
-      </c>
-      <c r="X24" s="3">
-        <v>-100</v>
       </c>
       <c r="Y24" s="3">
         <v>-100</v>
@@ -1931,10 +1977,13 @@
         <v>-100</v>
       </c>
       <c r="AA24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2010,162 +2059,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E26" s="3">
         <v>50100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-7200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-62700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-14500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-17800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-15300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-20100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>35800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-6500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-400</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-300</v>
       </c>
       <c r="Z26" s="3">
         <v>-300</v>
       </c>
       <c r="AA26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AB26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E27" s="3">
         <v>50100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-7200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-62700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-14500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-17800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-15300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-20100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>35800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-6500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2241,8 +2299,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2267,14 +2328,14 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>4</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -2286,40 +2347,43 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R29" s="3">
         <v>-100</v>
       </c>
       <c r="S29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T29" s="3">
         <v>-3700</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-7700</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W29" s="3">
         <v>-1600</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X29" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2395,8 +2459,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2472,56 +2539,59 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-10400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-800</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -2529,17 +2599,17 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>1200</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
@@ -2549,85 +2619,91 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E33" s="3">
         <v>50100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-7200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-62700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-14500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-17800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-15300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-20100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>35800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2200</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
       <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3">
         <v>-4100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-6500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2703,167 +2779,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E35" s="3">
         <v>50100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-7200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-62700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-14500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-17800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-15300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-20100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>35800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2200</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
       <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
         <v>-4100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-6500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>42825</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2891,8 +2976,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2920,139 +3006,143 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E41" s="3">
         <v>33100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>20800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>18500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>27900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>32700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>32300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>44300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>28100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>42400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>26500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>28300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2500</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
       <c r="U41" s="3">
+        <v>0</v>
+      </c>
+      <c r="V41" s="3">
         <v>400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6200</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>141300</v>
+      </c>
+      <c r="E42" s="3">
         <v>138200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>47700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>40200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>31600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>27100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>27600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>23300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>26900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>43900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>29000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>35000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>21000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>29400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>6200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>200</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3068,14 +3158,17 @@
       <c r="Y42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z42" s="3">
-        <v>0</v>
+      <c r="Z42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3083,10 +3176,10 @@
         <v>10200</v>
       </c>
       <c r="E43" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F43" s="3">
         <v>13900</v>
-      </c>
-      <c r="F43" s="3">
-        <v>700</v>
       </c>
       <c r="G43" s="3">
         <v>700</v>
@@ -3095,17 +3188,17 @@
         <v>700</v>
       </c>
       <c r="I43" s="3">
+        <v>700</v>
+      </c>
+      <c r="J43" s="3">
         <v>800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>200</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3121,38 +3214,41 @@
       <c r="Q43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T43" s="3">
+      <c r="R43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U43" s="3">
         <v>500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>700</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3228,56 +3324,59 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E45" s="3">
         <v>8100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>18900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2100</v>
       </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
       <c r="S45" s="3">
         <v>0</v>
       </c>
@@ -3285,137 +3384,143 @@
         <v>0</v>
       </c>
       <c r="U45" s="3">
+        <v>0</v>
+      </c>
+      <c r="V45" s="3">
         <v>100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>700</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>217200</v>
+      </c>
+      <c r="E46" s="3">
         <v>189500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>83300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>66500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>56000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>58700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>64400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>68400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>78400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>78300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>90300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>64600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>59600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>34500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>12100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>10100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>9600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7600</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E47" s="3">
         <v>7300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2400</v>
-      </c>
-      <c r="K47" s="3">
-        <v>300</v>
       </c>
       <c r="L47" s="3">
         <v>300</v>
       </c>
       <c r="M47" s="3">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="N47" s="3">
         <v>1000</v>
@@ -3426,8 +3531,8 @@
       <c r="P47" s="3">
         <v>1000</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>4</v>
+      <c r="Q47" s="3">
+        <v>1000</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>4</v>
@@ -3444,8 +3549,8 @@
       <c r="V47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
@@ -3459,70 +3564,73 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E48" s="3">
         <v>85000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>87700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>25100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>24500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>19000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>80700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>90000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>28700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>71600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>30000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>36000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>28200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>29800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4400</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
-      </c>
       <c r="U48" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="V48" s="3">
         <v>700</v>
       </c>
       <c r="W48" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="X48" s="3">
         <v>100</v>
@@ -3533,11 +3641,14 @@
       <c r="Z48" s="3">
         <v>100</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3613,8 +3724,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3690,8 +3804,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3767,85 +3884,91 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E52" s="3">
         <v>9200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>13300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>62300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>49900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>14400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1300</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S52" s="3">
+      <c r="S52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T52" s="3">
         <v>6900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1300</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3921,85 +4044,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>315500</v>
+      </c>
+      <c r="E54" s="3">
         <v>291100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>189300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>108700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>100400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>92200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>100400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>164700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>179000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>169600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>173700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>110400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>108100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>78100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>39900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>20600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>14000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>12500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>15300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>12900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>9000</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4027,8 +4156,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4056,62 +4186,63 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E57" s="3">
         <v>5600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2500</v>
-      </c>
-      <c r="P57" s="3">
-        <v>1400</v>
       </c>
       <c r="Q57" s="3">
         <v>1400</v>
       </c>
       <c r="R57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S57" s="3">
         <v>300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4124,8 +4255,8 @@
       <c r="X57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y57" s="3">
-        <v>0</v>
+      <c r="Y57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z57" s="3">
         <v>0</v>
@@ -4133,8 +4264,11 @@
       <c r="AA57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4168,18 +4302,18 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>4</v>
+      <c r="N58" s="3">
+        <v>0</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P58" s="3">
+      <c r="P58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q58" s="3">
         <v>1300</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4195,8 +4329,8 @@
       <c r="V58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -4210,162 +4344,171 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E59" s="3">
         <v>9800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>24800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>400</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>500</v>
       </c>
       <c r="R59" s="3">
         <v>500</v>
       </c>
       <c r="S59" s="3">
+        <v>500</v>
+      </c>
+      <c r="T59" s="3">
         <v>1100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2400</v>
-      </c>
-      <c r="V59" s="3">
-        <v>400</v>
       </c>
       <c r="W59" s="3">
         <v>400</v>
       </c>
       <c r="X59" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Y59" s="3">
         <v>500</v>
       </c>
       <c r="Z59" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA59" s="3">
         <v>400</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E60" s="3">
         <v>15400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>27100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2400</v>
-      </c>
-      <c r="V60" s="3">
-        <v>400</v>
       </c>
       <c r="W60" s="3">
         <v>400</v>
       </c>
       <c r="X60" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Y60" s="3">
         <v>500</v>
       </c>
       <c r="Z60" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA60" s="3">
         <v>400</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4441,52 +4584,55 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E62" s="3">
         <v>10600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9500</v>
-      </c>
-      <c r="F62" s="3">
-        <v>3200</v>
       </c>
       <c r="G62" s="3">
         <v>3200</v>
       </c>
       <c r="H62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I62" s="3">
         <v>3100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>3000</v>
       </c>
       <c r="J62" s="3">
         <v>3000</v>
       </c>
       <c r="K62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L62" s="3">
         <v>2900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>700</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
+      <c r="Q62" s="3">
+        <v>0</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>4</v>
@@ -4503,8 +4649,8 @@
       <c r="V62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
+      <c r="W62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X62" s="3">
         <v>0</v>
@@ -4518,8 +4664,11 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4595,8 +4744,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4672,8 +4824,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4749,85 +4904,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E66" s="3">
         <v>25900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>36600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1300</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4855,8 +5016,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4932,8 +5094,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5009,8 +5174,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5048,7 +5216,7 @@
         <v>9100</v>
       </c>
       <c r="O70" s="3">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="P70" s="3">
         <v>0</v>
@@ -5086,8 +5254,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5163,85 +5334,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-87600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-75600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-146900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-144100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-136900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-134500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-131400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-62500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-48200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-30100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-26100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-10400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>18700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>20100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-15700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-18400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-17900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-13800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-10800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-4300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-200</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5317,8 +5494,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5394,8 +5574,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5471,85 +5654,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>286200</v>
+      </c>
+      <c r="E76" s="3">
         <v>256100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>143700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>94200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>82700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>77900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>80900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>149200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>162900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>152800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>156400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>97000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>104800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>75000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>38000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>11800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7700</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5625,167 +5814,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>42825</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E81" s="3">
         <v>50100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-7200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-62700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-14500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-17800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-15300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-20100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>35800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2200</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
       <c r="S81" s="3">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3">
         <v>-4100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-6500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5813,70 +6011,71 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E83" s="3">
         <v>6800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>100</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
       <c r="U83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V83" s="3">
         <v>100</v>
       </c>
       <c r="W83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
@@ -5890,8 +6089,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5967,8 +6169,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6044,8 +6249,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6121,8 +6329,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6198,8 +6409,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6275,85 +6489,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-20900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>24300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-9000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2300</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-2500</v>
       </c>
       <c r="Q89" s="3">
         <v>-2500</v>
       </c>
       <c r="R89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="S89" s="3">
         <v>-7700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-5100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-500</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6381,26 +6601,27 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-58400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
@@ -6408,44 +6629,44 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-8300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-46000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>6700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V91" s="3">
+      <c r="V91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W91" s="3">
         <v>-800</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
@@ -6456,10 +6677,13 @@
         <v>0</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6535,8 +6759,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6612,71 +6839,74 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-58400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2500</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-18300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-43700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>8600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-10700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-900</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="V94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W94" s="3">
         <v>-3300</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
@@ -6687,10 +6917,13 @@
         <v>0</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6718,8 +6951,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6795,8 +7029,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6872,8 +7109,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6949,8 +7189,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7026,85 +7269,91 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E100" s="3">
         <v>38700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>30100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>16300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>21000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>71700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>28500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-8300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>6500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>13500</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W100" s="3">
         <v>5900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>5700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-400</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7163,98 +7412,104 @@
         <v>0</v>
       </c>
       <c r="V101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W101" s="3">
         <v>-100</v>
       </c>
       <c r="X101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y101" s="3">
         <v>300</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>100</v>
       </c>
       <c r="Z101" s="3">
         <v>100</v>
       </c>
       <c r="AA101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E102" s="3">
         <v>17300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-12000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>16200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>15900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>28000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>5100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>6700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BTBT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BTBT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
   <si>
     <t>BTBT</t>
   </si>
@@ -656,269 +656,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43100</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>42916</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42825</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E8" s="3">
         <v>29000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>30300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>28300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>44000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>20400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>700</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
       <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
         <v>4500</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
       <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
         <v>4900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4200</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>1400</v>
       </c>
       <c r="AA8" s="3">
         <v>1400</v>
       </c>
       <c r="AB8" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AC8" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E9" s="3">
         <v>15200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>700</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V9" s="3">
-        <v>0</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>4</v>
+      <c r="V9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W9" s="3">
+        <v>0</v>
       </c>
       <c r="X9" s="3" t="s">
         <v>4</v>
@@ -935,71 +942,74 @@
       <c r="AB9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E10" s="3">
         <v>13800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>14100</v>
       </c>
-      <c r="F10" s="3">
-        <v>6200</v>
-      </c>
       <c r="G10" s="3">
+        <v>6100</v>
+      </c>
+      <c r="H10" s="3">
         <v>2800</v>
       </c>
-      <c r="H10" s="3">
-        <v>3300</v>
-      </c>
       <c r="I10" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J10" s="3">
         <v>3100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>7800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>17400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>31500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>7000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1700</v>
       </c>
-      <c r="T10" s="3">
-        <v>0</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="U10" s="3">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W10" s="3">
         <v>4500</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1015,8 +1025,11 @@
       <c r="AB10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1045,8 +1058,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1104,29 +1118,32 @@
       <c r="U12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V12" s="3">
+      <c r="V12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W12" s="3">
         <v>400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>200</v>
-      </c>
-      <c r="X12" s="3">
-        <v>300</v>
       </c>
       <c r="Y12" s="3">
         <v>300</v>
       </c>
       <c r="Z12" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AA12" s="3">
         <v>100</v>
       </c>
       <c r="AB12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC12" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1205,53 +1222,56 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+        <v>1000</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F14" s="3">
-        <v>2900</v>
+        <v>-500</v>
       </c>
       <c r="G14" s="3">
         <v>2100</v>
       </c>
       <c r="H14" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I14" s="3">
-        <v>2200</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>48600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>27000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>14700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>18900</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>9000</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1267,8 +1287,8 @@
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1285,73 +1305,76 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E15" s="3">
         <v>8300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>6800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>9400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>9300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>100</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
-      </c>
-      <c r="V15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W15" s="3">
-        <v>0</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>4</v>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>4</v>
@@ -1359,14 +1382,17 @@
       <c r="Z15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
+      <c r="AA15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1392,168 +1418,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>40500</v>
+        <v>37500</v>
       </c>
       <c r="E17" s="3">
-        <v>-16800</v>
+        <v>29000</v>
       </c>
       <c r="F17" s="3">
-        <v>20000</v>
+        <v>29000</v>
       </c>
       <c r="G17" s="3">
-        <v>18600</v>
+        <v>25600</v>
       </c>
       <c r="H17" s="3">
-        <v>11700</v>
+        <v>17300</v>
       </c>
       <c r="I17" s="3">
-        <v>11300</v>
+        <v>14800</v>
       </c>
       <c r="J17" s="3">
+        <v>14000</v>
+      </c>
+      <c r="K17" s="3">
         <v>70300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>24700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>19300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>26000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>26600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4700</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>1800</v>
       </c>
       <c r="AA17" s="3">
         <v>1800</v>
       </c>
       <c r="AB17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AC17" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-11500</v>
+        <v>-14800</v>
       </c>
       <c r="E18" s="3">
-        <v>47100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3">
-        <v>-3900</v>
+        <v>1300</v>
       </c>
       <c r="G18" s="3">
-        <v>-7000</v>
+        <v>-9600</v>
       </c>
       <c r="H18" s="3">
-        <v>-2700</v>
+        <v>-5700</v>
       </c>
       <c r="I18" s="3">
-        <v>-3000</v>
+        <v>-5700</v>
       </c>
       <c r="J18" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="K18" s="3">
         <v>-62500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-14400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-17900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-15600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>25700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-500</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-400</v>
       </c>
       <c r="AA18" s="3">
         <v>-400</v>
       </c>
       <c r="AB18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AC18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1582,59 +1615,60 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>11500</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-49800</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
-        <v>4600</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>400</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="M20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N20" s="3">
+        <v>600</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="P20" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="R20" s="3">
+        <v>10400</v>
+      </c>
+      <c r="S20" s="3">
         <v>800</v>
       </c>
-      <c r="J20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>1300</v>
-      </c>
-      <c r="M20" s="3">
-        <v>600</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>10400</v>
-      </c>
-      <c r="R20" s="3">
-        <v>800</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1642,17 +1676,17 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-1200</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
@@ -1662,76 +1696,79 @@
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-3100</v>
+        <v>-28900</v>
       </c>
       <c r="E21" s="3">
-        <v>58500</v>
+        <v>-3200</v>
       </c>
       <c r="F21" s="3">
-        <v>1400</v>
+        <v>58000</v>
       </c>
       <c r="G21" s="3">
-        <v>-3500</v>
+        <v>3600</v>
       </c>
       <c r="H21" s="3">
-        <v>1400</v>
+        <v>-3400</v>
       </c>
       <c r="I21" s="3">
         <v>1400</v>
       </c>
       <c r="J21" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K21" s="3">
         <v>-53900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-11300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-9500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-15400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>39700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-6400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-700</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>-400</v>
       </c>
       <c r="Z21" s="3">
         <v>-400</v>
@@ -1740,33 +1777,36 @@
         <v>-400</v>
       </c>
       <c r="AB21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AC21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1822,102 +1862,108 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-38200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-11400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>51700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-63300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-14300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-16600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-12800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-19200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>36100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-500</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-400</v>
       </c>
       <c r="AA23" s="3">
         <v>-400</v>
       </c>
       <c r="AB23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AC23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1600</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H24" s="3">
         <v>100</v>
@@ -1926,32 +1972,32 @@
         <v>100</v>
       </c>
       <c r="J24" s="3">
+        <v>100</v>
+      </c>
+      <c r="K24" s="3">
         <v>-600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -1961,17 +2007,17 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W24" s="3">
-        <v>0</v>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>100</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>-100</v>
       </c>
       <c r="Z24" s="3">
         <v>-100</v>
@@ -1980,10 +2026,13 @@
         <v>-100</v>
       </c>
       <c r="AB24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2062,168 +2111,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>50100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-7200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-62700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-14500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-17800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-15300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-20100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>35800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-6500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-400</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-300</v>
       </c>
       <c r="AA26" s="3">
         <v>-300</v>
       </c>
       <c r="AB26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AC26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>50100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-62700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-14500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-17800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-15300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-20100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>35800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-6500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2302,8 +2360,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2331,14 +2392,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>4</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -2350,40 +2411,43 @@
         <v>0</v>
       </c>
       <c r="R29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S29" s="3">
         <v>-100</v>
       </c>
       <c r="T29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U29" s="3">
         <v>-3700</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-7700</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X29" s="3">
         <v>-1600</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y29" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2462,8 +2526,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2542,59 +2609,62 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-22500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="F32" s="3">
+        <v>49800</v>
+      </c>
+      <c r="G32" s="3">
+        <v>9700</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I32" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J32" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K32" s="3">
+        <v>700</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="G32" s="3">
-        <v>100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="M32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O32" s="3">
+        <v>6900</v>
+      </c>
+      <c r="P32" s="3">
+        <v>3700</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="S32" s="3">
         <v>-800</v>
       </c>
-      <c r="J32" s="3">
-        <v>700</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="N32" s="3">
-        <v>6900</v>
-      </c>
-      <c r="O32" s="3">
-        <v>3700</v>
-      </c>
-      <c r="P32" s="3">
-        <v>2900</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-10400</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2602,17 +2672,17 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>1200</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
@@ -2622,88 +2692,94 @@
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>50100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-62700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-14500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-17800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-15300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-20100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>35800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2200</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
         <v>-4100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2782,173 +2858,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>50100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-62700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-14500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-17800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-15300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-20100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>35800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2200</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
         <v>-4100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43100</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>42916</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42825</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2977,8 +3062,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3007,145 +3093,149 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>103200</v>
+      </c>
+      <c r="E41" s="3">
         <v>59000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>33100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>18500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>27900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>32700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>32300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>44300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>28100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>42400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>26500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>28300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2500</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
       <c r="V41" s="3">
+        <v>0</v>
+      </c>
+      <c r="W41" s="3">
         <v>400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6200</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>141300</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>138200</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>47700</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>40200</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>31600</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>27100</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>27600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>23300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>26900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>43900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>29000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>35000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>21000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>29400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>6200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>200</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3161,28 +3251,31 @@
       <c r="Z42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>10200</v>
+        <v>13500</v>
       </c>
       <c r="E43" s="3">
-        <v>10200</v>
+        <v>11300</v>
       </c>
       <c r="F43" s="3">
+        <v>11200</v>
+      </c>
+      <c r="G43" s="3">
         <v>13900</v>
-      </c>
-      <c r="G43" s="3">
-        <v>700</v>
       </c>
       <c r="H43" s="3">
         <v>700</v>
@@ -3191,17 +3284,17 @@
         <v>700</v>
       </c>
       <c r="J43" s="3">
+        <v>700</v>
+      </c>
+      <c r="K43" s="3">
         <v>800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>200</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3217,61 +3310,64 @@
       <c r="R43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U43" s="3">
+      <c r="S43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V43" s="3">
         <v>500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>700</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3327,59 +3423,62 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>6600</v>
+        <v>121400</v>
       </c>
       <c r="E45" s="3">
-        <v>8100</v>
+        <v>142600</v>
       </c>
       <c r="F45" s="3">
+        <v>140900</v>
+      </c>
+      <c r="G45" s="3">
+        <v>49800</v>
+      </c>
+      <c r="H45" s="3">
+        <v>42100</v>
+      </c>
+      <c r="I45" s="3">
+        <v>34700</v>
+      </c>
+      <c r="J45" s="3">
+        <v>28400</v>
+      </c>
+      <c r="K45" s="3">
+        <v>3400</v>
+      </c>
+      <c r="L45" s="3">
+        <v>12700</v>
+      </c>
+      <c r="M45" s="3">
+        <v>7000</v>
+      </c>
+      <c r="N45" s="3">
+        <v>6300</v>
+      </c>
+      <c r="O45" s="3">
+        <v>18900</v>
+      </c>
+      <c r="P45" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>10400</v>
+      </c>
+      <c r="R45" s="3">
         <v>4900</v>
       </c>
-      <c r="G45" s="3">
-        <v>4800</v>
-      </c>
-      <c r="H45" s="3">
-        <v>5200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>3400</v>
-      </c>
-      <c r="K45" s="3">
-        <v>12700</v>
-      </c>
-      <c r="L45" s="3">
-        <v>7000</v>
-      </c>
-      <c r="M45" s="3">
-        <v>6300</v>
-      </c>
-      <c r="N45" s="3">
-        <v>18900</v>
-      </c>
-      <c r="O45" s="3">
-        <v>3100</v>
-      </c>
-      <c r="P45" s="3">
-        <v>10400</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>4900</v>
-      </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2100</v>
       </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
       <c r="T45" s="3">
         <v>0</v>
       </c>
@@ -3387,116 +3486,122 @@
         <v>0</v>
       </c>
       <c r="V45" s="3">
+        <v>0</v>
+      </c>
+      <c r="W45" s="3">
         <v>100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>4300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>700</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>258500</v>
+      </c>
+      <c r="E46" s="3">
         <v>217200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>189500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>83300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>66500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>56000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>58700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>64400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>68400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>78400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>78300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>90300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>64600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>59600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>34500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>12100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>10100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>9600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7600</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>8200</v>
+        <v>28700</v>
       </c>
       <c r="E47" s="3">
-        <v>7300</v>
+        <v>6000</v>
       </c>
       <c r="F47" s="3">
         <v>4800</v>
@@ -3505,25 +3610,25 @@
         <v>4400</v>
       </c>
       <c r="H47" s="3">
-        <v>5400</v>
+        <v>4000</v>
       </c>
       <c r="I47" s="3">
-        <v>4300</v>
+        <v>3900</v>
       </c>
       <c r="J47" s="3">
+        <v>3900</v>
+      </c>
+      <c r="K47" s="3">
         <v>1800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2400</v>
-      </c>
-      <c r="L47" s="3">
-        <v>300</v>
       </c>
       <c r="M47" s="3">
         <v>300</v>
       </c>
       <c r="N47" s="3">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="O47" s="3">
         <v>1000</v>
@@ -3534,8 +3639,8 @@
       <c r="Q47" s="3">
         <v>1000</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>4</v>
+      <c r="R47" s="3">
+        <v>1000</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>4</v>
@@ -3552,8 +3657,8 @@
       <c r="W47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -3567,73 +3672,76 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>77800</v>
+      </c>
+      <c r="E48" s="3">
         <v>79000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>85000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>87700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>25100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>24500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>19000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>80700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>90000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>28700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>71600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>30000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>36000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>28200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>29800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>17700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4400</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
-      </c>
       <c r="V48" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="W48" s="3">
         <v>700</v>
       </c>
       <c r="X48" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="Y48" s="3">
         <v>100</v>
@@ -3644,11 +3752,14 @@
       <c r="AA48" s="3">
         <v>100</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3727,8 +3838,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3807,8 +3921,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3887,88 +4004,94 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>11100</v>
+        <v>7000</v>
       </c>
       <c r="E52" s="3">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F52" s="3">
-        <v>13500</v>
+        <v>7300</v>
       </c>
       <c r="G52" s="3">
+        <v>11600</v>
+      </c>
+      <c r="H52" s="3">
         <v>12800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>62300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>49900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>14800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>14400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1300</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T52" s="3">
+      <c r="T52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U52" s="3">
         <v>6900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1300</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4047,88 +4170,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>376000</v>
+      </c>
+      <c r="E54" s="3">
         <v>315500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>291100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>189300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>108700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>100400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>92200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>100400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>164700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>179000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>169600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>173700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>110400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>108100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>78100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>39900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>20600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>14000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>12500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>15300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>12900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>9000</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4157,8 +4286,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4187,65 +4317,66 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E57" s="3">
         <v>3200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2500</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>1400</v>
       </c>
       <c r="R57" s="3">
         <v>1400</v>
       </c>
       <c r="S57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="T57" s="3">
         <v>300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>100</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4258,8 +4389,8 @@
       <c r="Y57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z57" s="3">
-        <v>0</v>
+      <c r="Z57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA57" s="3">
         <v>0</v>
@@ -4267,22 +4398,25 @@
       <c r="AB57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -4305,18 +4439,18 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R58" s="3">
         <v>1300</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4332,8 +4466,8 @@
       <c r="W58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -4347,182 +4481,191 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>7100</v>
+        <v>41100</v>
       </c>
       <c r="E59" s="3">
-        <v>9800</v>
+        <v>5100</v>
       </c>
       <c r="F59" s="3">
-        <v>24800</v>
+        <v>7800</v>
       </c>
       <c r="G59" s="3">
+        <v>22900</v>
+      </c>
+      <c r="H59" s="3">
         <v>1100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>400</v>
-      </c>
-      <c r="R59" s="3">
-        <v>500</v>
       </c>
       <c r="S59" s="3">
         <v>500</v>
       </c>
       <c r="T59" s="3">
+        <v>500</v>
+      </c>
+      <c r="U59" s="3">
         <v>1100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2400</v>
-      </c>
-      <c r="W59" s="3">
-        <v>400</v>
       </c>
       <c r="X59" s="3">
         <v>400</v>
       </c>
       <c r="Y59" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Z59" s="3">
         <v>500</v>
       </c>
       <c r="AA59" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB59" s="3">
         <v>400</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E60" s="3">
         <v>10300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>27100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2400</v>
-      </c>
-      <c r="W60" s="3">
-        <v>400</v>
       </c>
       <c r="X60" s="3">
         <v>400</v>
       </c>
       <c r="Y60" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Z60" s="3">
         <v>500</v>
       </c>
       <c r="AA60" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB60" s="3">
         <v>400</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -4587,55 +4730,58 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10000</v>
+        <v>3200</v>
       </c>
       <c r="E62" s="3">
-        <v>10600</v>
+        <v>5100</v>
       </c>
       <c r="F62" s="3">
-        <v>9500</v>
+        <v>5100</v>
       </c>
       <c r="G62" s="3">
-        <v>3200</v>
+        <v>5100</v>
       </c>
       <c r="H62" s="3">
         <v>3200</v>
       </c>
       <c r="I62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J62" s="3">
         <v>3100</v>
-      </c>
-      <c r="J62" s="3">
-        <v>3000</v>
       </c>
       <c r="K62" s="3">
         <v>3000</v>
       </c>
       <c r="L62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M62" s="3">
         <v>2900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>700</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>4</v>
+      <c r="R62" s="3">
+        <v>0</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>4</v>
@@ -4652,8 +4798,8 @@
       <c r="W62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
+      <c r="X62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y62" s="3">
         <v>0</v>
@@ -4667,8 +4813,11 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4747,8 +4896,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4827,8 +4979,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4907,88 +5062,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E66" s="3">
         <v>20200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>36600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1300</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5017,8 +5178,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5097,8 +5259,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5177,8 +5342,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5219,7 +5387,7 @@
         <v>9100</v>
       </c>
       <c r="P70" s="3">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="Q70" s="3">
         <v>0</v>
@@ -5257,8 +5425,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5337,88 +5508,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-126400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-87600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-75600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-146900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-144100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-136900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-134500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-131400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-62500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-48200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-30100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-26100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-10400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>18700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>20100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-15700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-18400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-17900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-13800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-10800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-4300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-200</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5497,8 +5674,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5577,8 +5757,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5657,88 +5840,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>306000</v>
+      </c>
+      <c r="E76" s="3">
         <v>286200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>256100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>143700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>94200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>82700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>77900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>80900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>149200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>162900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>152800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>156400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>97000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>104800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>75000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>38000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>11600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7700</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5817,173 +6006,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43100</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>42916</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42825</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>50100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-62700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-14500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-17800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-15300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-20100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>35800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2200</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>-4100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6012,73 +6210,74 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>8300</v>
+        <v>3600</v>
       </c>
       <c r="E83" s="3">
-        <v>6800</v>
+        <v>3700</v>
       </c>
       <c r="F83" s="3">
-        <v>3400</v>
+        <v>3600</v>
       </c>
       <c r="G83" s="3">
-        <v>3600</v>
+        <v>9400</v>
       </c>
       <c r="H83" s="3">
+        <v>9300</v>
+      </c>
+      <c r="I83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="J83" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K83" s="3">
+        <v>9400</v>
+      </c>
+      <c r="L83" s="3">
+        <v>9300</v>
+      </c>
+      <c r="M83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="N83" s="3">
+        <v>3800</v>
+      </c>
+      <c r="O83" s="3">
+        <v>3300</v>
+      </c>
+      <c r="P83" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="R83" s="3">
         <v>3700</v>
       </c>
-      <c r="I83" s="3">
-        <v>3600</v>
-      </c>
-      <c r="J83" s="3">
-        <v>9400</v>
-      </c>
-      <c r="K83" s="3">
-        <v>9300</v>
-      </c>
-      <c r="L83" s="3">
-        <v>5300</v>
-      </c>
-      <c r="M83" s="3">
-        <v>3800</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="S83" s="3">
         <v>3300</v>
       </c>
-      <c r="O83" s="3">
-        <v>3800</v>
-      </c>
-      <c r="P83" s="3">
-        <v>2300</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>3700</v>
-      </c>
-      <c r="R83" s="3">
-        <v>3300</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>100</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
       <c r="V83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W83" s="3">
         <v>100</v>
       </c>
       <c r="X83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
@@ -6092,8 +6291,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6172,8 +6374,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6252,8 +6457,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6332,8 +6540,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6412,8 +6623,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6492,88 +6706,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-20900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>24300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2300</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-2500</v>
       </c>
       <c r="R89" s="3">
         <v>-2500</v>
       </c>
       <c r="S89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="T89" s="3">
         <v>-7700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-5100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-500</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
       <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6602,29 +6822,30 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-58400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
@@ -6632,44 +6853,44 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-8300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-46000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>6700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X91" s="3">
         <v>-800</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
@@ -6680,10 +6901,13 @@
         <v>0</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6762,8 +6986,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6842,74 +7069,77 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-58400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2500</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-18300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>3800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-43700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>8600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-10700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-900</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X94" s="3">
         <v>-3300</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
         <v>0</v>
       </c>
@@ -6920,10 +7150,13 @@
         <v>0</v>
       </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6952,31 +7185,32 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7032,8 +7266,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7112,8 +7349,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7192,8 +7432,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7272,111 +7515,117 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E100" s="3">
         <v>41600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>38700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>30100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>16300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>21000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>71700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>4700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>28500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-8300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>6500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>13500</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X100" s="3">
         <v>5900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>5700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-400</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7415,101 +7664,107 @@
         <v>0</v>
       </c>
       <c r="W101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X101" s="3">
         <v>-100</v>
       </c>
       <c r="Y101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z101" s="3">
         <v>300</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>100</v>
       </c>
       <c r="AA101" s="3">
         <v>100</v>
       </c>
       <c r="AB101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E102" s="3">
         <v>25900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>17300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-12000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>16200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>15900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>28000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>6700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BTBT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BTBT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="92">
   <si>
     <t>BTBT</t>
   </si>
@@ -656,279 +656,285 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42916</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42825</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E8" s="3">
         <v>22700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>29000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>30300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>16100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>13400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>28300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>44000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>20400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>700</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
-      </c>
       <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
         <v>4500</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
-      </c>
       <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
         <v>4900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4200</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>1400</v>
       </c>
       <c r="AB8" s="3">
         <v>1400</v>
       </c>
       <c r="AC8" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AD8" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E9" s="3">
         <v>15500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>16200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>700</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W9" s="3">
-        <v>0</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>4</v>
+      <c r="W9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X9" s="3">
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>4</v>
@@ -945,74 +951,77 @@
       <c r="AC9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E10" s="3">
         <v>7200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>13800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>14100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>7800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>17400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>31500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>7000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1700</v>
       </c>
-      <c r="U10" s="3">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W10" s="3">
+      <c r="V10" s="3">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X10" s="3">
         <v>4500</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1028,8 +1037,11 @@
       <c r="AC10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1059,8 +1071,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1121,29 +1134,32 @@
       <c r="V12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W12" s="3">
+      <c r="W12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X12" s="3">
         <v>400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>200</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>300</v>
       </c>
       <c r="Z12" s="3">
         <v>300</v>
       </c>
       <c r="AA12" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AB12" s="3">
         <v>100</v>
       </c>
       <c r="AC12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD12" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1225,56 +1241,59 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E14" s="3">
         <v>1000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
         <v>-500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2100</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>48600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>27000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>14700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>18900</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>9000</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1290,8 +1309,8 @@
       <c r="W14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1308,76 +1327,79 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E15" s="3">
         <v>8400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>9400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>9300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>100</v>
       </c>
-      <c r="V15" s="3">
-        <v>0</v>
-      </c>
-      <c r="W15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3" t="s">
-        <v>4</v>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>4</v>
@@ -1385,14 +1407,17 @@
       <c r="AA15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB15" s="3">
-        <v>0</v>
+      <c r="AB15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1419,174 +1444,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>37500</v>
+        <v>-2700</v>
       </c>
       <c r="E17" s="3">
-        <v>29000</v>
+        <v>59500</v>
       </c>
       <c r="F17" s="3">
-        <v>29000</v>
+        <v>40500</v>
       </c>
       <c r="G17" s="3">
-        <v>25600</v>
+        <v>-16800</v>
       </c>
       <c r="H17" s="3">
-        <v>17300</v>
+        <v>17900</v>
       </c>
       <c r="I17" s="3">
-        <v>14800</v>
+        <v>18600</v>
       </c>
       <c r="J17" s="3">
+        <v>11700</v>
+      </c>
+      <c r="K17" s="3">
         <v>14000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>70300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>24700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>19300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>26000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>26600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4700</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>1800</v>
       </c>
       <c r="AB17" s="3">
         <v>1800</v>
       </c>
       <c r="AC17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AD17" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-14800</v>
+        <v>28300</v>
       </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <v>-36700</v>
       </c>
       <c r="F18" s="3">
-        <v>1300</v>
+        <v>-11600</v>
       </c>
       <c r="G18" s="3">
-        <v>-9600</v>
+        <v>47100</v>
       </c>
       <c r="H18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="K18" s="3">
         <v>-5700</v>
       </c>
-      <c r="I18" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-62500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-14400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-17900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>25700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-500</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-400</v>
       </c>
       <c r="AB18" s="3">
         <v>-400</v>
       </c>
       <c r="AC18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AD18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1616,62 +1648,63 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>22500</v>
+        <v>-4900</v>
       </c>
       <c r="E20" s="3">
-        <v>11500</v>
+        <v>600</v>
       </c>
       <c r="F20" s="3">
-        <v>-49800</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
-        <v>-9700</v>
+        <v>-4000</v>
       </c>
       <c r="H20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M20" s="3">
+        <v>100</v>
+      </c>
+      <c r="N20" s="3">
         <v>1300</v>
       </c>
-      <c r="I20" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>1300</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-6900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>10400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>800</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1679,17 +1712,17 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-1200</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
@@ -1699,79 +1732,82 @@
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-28900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>58000</v>
       </c>
-      <c r="G21" s="3">
-        <v>3600</v>
-      </c>
       <c r="H21" s="3">
+        <v>3900</v>
+      </c>
+      <c r="I21" s="3">
         <v>-3400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-53900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-11300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-9500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-15400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>39700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-6400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-700</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>-400</v>
       </c>
       <c r="AA21" s="3">
         <v>-400</v>
@@ -1780,10 +1816,13 @@
         <v>-400</v>
       </c>
       <c r="AC21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AD21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1808,8 +1847,8 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1865,108 +1904,114 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-38200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-11400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>51700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-63300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-16600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-12800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-19200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>36100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-500</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-400</v>
       </c>
       <c r="AB23" s="3">
         <v>-400</v>
       </c>
       <c r="AC23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AD23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1600</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3">
         <v>100</v>
@@ -1975,32 +2020,32 @@
         <v>100</v>
       </c>
       <c r="K24" s="3">
+        <v>100</v>
+      </c>
+      <c r="L24" s="3">
         <v>-600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
@@ -2010,17 +2055,17 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X24" s="3">
-        <v>0</v>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>100</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>-100</v>
       </c>
       <c r="AA24" s="3">
         <v>-100</v>
@@ -2029,10 +2074,13 @@
         <v>-100</v>
       </c>
       <c r="AC24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2114,174 +2162,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-38800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>50100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-62700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-14500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-17800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-15300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>35800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-6500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-400</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-300</v>
       </c>
       <c r="AB26" s="3">
         <v>-300</v>
       </c>
       <c r="AC26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AD26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-38800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>50100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-62700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-17800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-15300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>35800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-6500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2363,8 +2420,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2395,14 +2455,14 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>4</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -2414,40 +2474,43 @@
         <v>0</v>
       </c>
       <c r="S29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T29" s="3">
         <v>-100</v>
       </c>
       <c r="U29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V29" s="3">
         <v>-3700</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-7700</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z29" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="AB29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2529,8 +2592,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2612,62 +2678,65 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-22500</v>
+        <v>4900</v>
       </c>
       <c r="E32" s="3">
-        <v>-11500</v>
+        <v>-600</v>
       </c>
       <c r="F32" s="3">
-        <v>49800</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3">
-        <v>9700</v>
+        <v>4000</v>
       </c>
       <c r="H32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>300</v>
+      </c>
+      <c r="K32" s="3">
+        <v>3400</v>
+      </c>
+      <c r="L32" s="3">
+        <v>700</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N32" s="3">
         <v>-1300</v>
       </c>
-      <c r="I32" s="3">
-        <v>3400</v>
-      </c>
-      <c r="J32" s="3">
-        <v>3400</v>
-      </c>
-      <c r="K32" s="3">
-        <v>700</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>6900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-10400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-800</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -2675,17 +2744,17 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>1200</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
@@ -2695,91 +2764,97 @@
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-38800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>50100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-62700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-17800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-15300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>35800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2200</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3">
         <v>-4100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-9500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-6500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2861,179 +2936,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-38800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>50100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-62700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-17800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-15300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>35800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2200</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
         <v>-4100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-9500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-6500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42916</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42825</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3063,8 +3147,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3094,91 +3179,95 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>95200</v>
+      </c>
+      <c r="E41" s="3">
         <v>103200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>59000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>33100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>20800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>18500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>27900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>32700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>32300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>44300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>28100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>42400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>26500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>28300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2500</v>
       </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
       <c r="W41" s="3">
+        <v>0</v>
+      </c>
+      <c r="X41" s="3">
         <v>400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>10000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6200</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3204,41 +3293,41 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>27600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>23300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>26900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>43900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>29000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>35000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>21000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>29400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>6200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>200</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3254,31 +3343,34 @@
       <c r="AA42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
+      <c r="AB42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E43" s="3">
         <v>13500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13900</v>
-      </c>
-      <c r="H43" s="3">
-        <v>700</v>
       </c>
       <c r="I43" s="3">
         <v>700</v>
@@ -3287,17 +3379,17 @@
         <v>700</v>
       </c>
       <c r="K43" s="3">
+        <v>700</v>
+      </c>
+      <c r="L43" s="3">
         <v>800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>200</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3313,38 +3405,41 @@
       <c r="S43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V43" s="3">
+      <c r="T43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W43" s="3">
         <v>500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>700</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3369,8 +3464,8 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3426,62 +3521,65 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>164700</v>
+      </c>
+      <c r="E45" s="3">
         <v>121400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>142600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>140900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>49800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>42100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>34700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>28400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>12700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>18900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2100</v>
       </c>
-      <c r="T45" s="3">
-        <v>0</v>
-      </c>
       <c r="U45" s="3">
         <v>0</v>
       </c>
@@ -3489,149 +3587,155 @@
         <v>0</v>
       </c>
       <c r="W45" s="3">
+        <v>0</v>
+      </c>
+      <c r="X45" s="3">
         <v>100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>700</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>296900</v>
+      </c>
+      <c r="E46" s="3">
         <v>258500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>217200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>189500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>83300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>66500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>56000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>58700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>64400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>68400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>78400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>78300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>90300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>64600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>59600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>34500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>12100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>10100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>9600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7600</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E47" s="3">
         <v>28700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>3900</v>
       </c>
       <c r="J47" s="3">
         <v>3900</v>
       </c>
       <c r="K47" s="3">
+        <v>3900</v>
+      </c>
+      <c r="L47" s="3">
         <v>1800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2400</v>
-      </c>
-      <c r="M47" s="3">
-        <v>300</v>
       </c>
       <c r="N47" s="3">
         <v>300</v>
       </c>
       <c r="O47" s="3">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="P47" s="3">
         <v>1000</v>
@@ -3642,8 +3746,8 @@
       <c r="R47" s="3">
         <v>1000</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>4</v>
+      <c r="S47" s="3">
+        <v>1000</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>4</v>
@@ -3660,8 +3764,8 @@
       <c r="X47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -3675,76 +3779,79 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>122300</v>
+      </c>
+      <c r="E48" s="3">
         <v>77800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>79000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>85000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>87700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>25100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>24500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>80700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>90000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>28700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>71600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>30000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>36000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>28200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>29800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>17700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4400</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
-      </c>
       <c r="W48" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="X48" s="3">
         <v>700</v>
       </c>
       <c r="Y48" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="Z48" s="3">
         <v>100</v>
@@ -3755,16 +3862,19 @@
       <c r="AB48" s="3">
         <v>100</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>32400</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
@@ -3841,8 +3951,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3924,8 +4037,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4007,91 +4123,97 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>47700</v>
+      </c>
+      <c r="E52" s="3">
         <v>7000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>13300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>62300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>49900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>14800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>11500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>14400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1300</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U52" s="3">
+      <c r="U52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V52" s="3">
         <v>6900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1300</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4173,91 +4295,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>538200</v>
+      </c>
+      <c r="E54" s="3">
         <v>376000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>315500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>291100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>189300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>108700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>100400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>92200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>100400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>164700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>179000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>169600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>173700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>110400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>108100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>78100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>39900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>20600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>12500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>15300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>12900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>13000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>9000</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4287,8 +4415,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4318,68 +4447,69 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E57" s="3">
         <v>3700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2500</v>
-      </c>
-      <c r="R57" s="3">
-        <v>1400</v>
       </c>
       <c r="S57" s="3">
         <v>1400</v>
       </c>
       <c r="T57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="U57" s="3">
         <v>300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>100</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4392,8 +4522,8 @@
       <c r="Z57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA57" s="3">
-        <v>0</v>
+      <c r="AA57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB57" s="3">
         <v>0</v>
@@ -4401,26 +4531,29 @@
       <c r="AC57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E58" s="3">
         <v>4100</v>
-      </c>
-      <c r="E58" s="3">
-        <v>2000</v>
       </c>
       <c r="F58" s="3">
         <v>2000</v>
       </c>
       <c r="G58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H58" s="3">
         <v>1900</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
@@ -4442,18 +4575,18 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
+      <c r="P58" s="3">
+        <v>0</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R58" s="3">
+      <c r="R58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S58" s="3">
         <v>1300</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4469,8 +4602,8 @@
       <c r="X58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -4484,192 +4617,201 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E59" s="3">
         <v>41100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>22900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>400</v>
-      </c>
-      <c r="S59" s="3">
-        <v>500</v>
       </c>
       <c r="T59" s="3">
         <v>500</v>
       </c>
       <c r="U59" s="3">
+        <v>500</v>
+      </c>
+      <c r="V59" s="3">
         <v>1100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2400</v>
-      </c>
-      <c r="X59" s="3">
-        <v>400</v>
       </c>
       <c r="Y59" s="3">
         <v>400</v>
       </c>
       <c r="Z59" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AA59" s="3">
         <v>500</v>
       </c>
       <c r="AB59" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC59" s="3">
         <v>400</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E60" s="3">
         <v>49000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>27100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2400</v>
-      </c>
-      <c r="X60" s="3">
-        <v>400</v>
       </c>
       <c r="Y60" s="3">
         <v>400</v>
       </c>
       <c r="Z60" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AA60" s="3">
         <v>500</v>
       </c>
       <c r="AB60" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC60" s="3">
         <v>400</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E61" s="3">
         <v>7200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4400</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -4733,16 +4875,19 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3200</v>
-      </c>
-      <c r="E62" s="3">
-        <v>5100</v>
       </c>
       <c r="F62" s="3">
         <v>5100</v>
@@ -4751,40 +4896,40 @@
         <v>5100</v>
       </c>
       <c r="H62" s="3">
-        <v>3200</v>
+        <v>5100</v>
       </c>
       <c r="I62" s="3">
         <v>3200</v>
       </c>
       <c r="J62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K62" s="3">
         <v>3100</v>
-      </c>
-      <c r="K62" s="3">
-        <v>3000</v>
       </c>
       <c r="L62" s="3">
         <v>3000</v>
       </c>
       <c r="M62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N62" s="3">
         <v>2900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>700</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>4</v>
+      <c r="S62" s="3">
+        <v>0</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>4</v>
@@ -4801,8 +4946,8 @@
       <c r="X62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z62" s="3">
         <v>0</v>
@@ -4816,8 +4961,11 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4899,8 +5047,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4982,8 +5133,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5065,91 +5219,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>74800</v>
+      </c>
+      <c r="E66" s="3">
         <v>61000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>20200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>36600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1300</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5179,8 +5339,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5262,8 +5423,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5345,8 +5509,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5390,7 +5557,7 @@
         <v>9100</v>
       </c>
       <c r="Q70" s="3">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="R70" s="3">
         <v>0</v>
@@ -5428,8 +5595,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5511,91 +5681,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-98200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-126400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-87600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-75600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-146900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-144100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-136900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-134500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-131400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-62500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-48200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-30100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-26100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-10400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>20100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-15700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-18400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-17900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-13800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-10800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-200</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5677,8 +5853,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5760,8 +5939,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5843,91 +6025,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>454400</v>
+      </c>
+      <c r="E76" s="3">
         <v>306000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>286200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>256100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>143700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>94200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>82700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>77900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>80900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>149200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>162900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>152800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>156400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>97000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>104800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>75000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>38000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>19900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>11600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7700</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6009,179 +6197,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42916</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42825</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-38800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>50100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-62700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-17800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-15300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>35800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2200</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3">
         <v>-4100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-9500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-6500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6211,76 +6408,77 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E83" s="3">
         <v>3600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>9300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>100</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
       <c r="W83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X83" s="3">
         <v>100</v>
       </c>
       <c r="Y83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
@@ -6294,8 +6492,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6377,8 +6578,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6460,8 +6664,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6543,8 +6750,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6626,8 +6836,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6709,91 +6922,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E89" s="3">
         <v>10100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-9500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-20900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>24300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-13900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-9000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-9700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2300</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-2500</v>
       </c>
       <c r="S89" s="3">
         <v>-2500</v>
       </c>
       <c r="T89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="U89" s="3">
         <v>-7700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-500</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
       <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6823,32 +7042,33 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-86800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-58400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
@@ -6856,44 +7076,44 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-8300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-46000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>6700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-11200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-800</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
@@ -6904,10 +7124,13 @@
         <v>0</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6989,8 +7212,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7072,77 +7298,80 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-125000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-58400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2500</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-18300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>3800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-43700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>1100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>8600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-10700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-900</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
@@ -7153,10 +7382,13 @@
         <v>0</v>
       </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7186,8 +7418,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7212,8 +7445,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7269,8 +7502,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7352,8 +7588,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7435,8 +7674,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7518,91 +7760,97 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>111100</v>
+      </c>
+      <c r="E100" s="3">
         <v>51400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>41600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>38700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>30100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>16300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>6700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>21000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>71700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>28500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-8300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>6500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>13500</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y100" s="3">
         <v>5900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>5700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-400</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7627,8 +7875,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -7667,104 +7915,110 @@
         <v>0</v>
       </c>
       <c r="X101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y101" s="3">
         <v>-100</v>
       </c>
       <c r="Z101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA101" s="3">
         <v>300</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>100</v>
       </c>
       <c r="AB101" s="3">
         <v>100</v>
       </c>
       <c r="AC101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E102" s="3">
         <v>44200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>25900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>17300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-12000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>16200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>15900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>28000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>6700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BTBT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BTBT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
   <si>
     <t>BTBT</t>
   </si>
@@ -656,288 +656,295 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E8" s="3">
         <v>25600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>22700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>29000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>30300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>16100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>13400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>28300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>44000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>20400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>700</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
       <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
         <v>4500</v>
       </c>
-      <c r="Y8" s="3">
-        <v>0</v>
-      </c>
       <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="3">
         <v>4900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4200</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>1400</v>
       </c>
       <c r="AC8" s="3">
         <v>1400</v>
       </c>
       <c r="AD8" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AE8" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E9" s="3">
         <v>15600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>16200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>9900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>13400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>6200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>700</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X9" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3" t="s">
-        <v>4</v>
+      <c r="X9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>0</v>
       </c>
       <c r="Z9" s="3" t="s">
         <v>4</v>
@@ -954,77 +961,80 @@
       <c r="AD9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E10" s="3">
         <v>10000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>14100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>8600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>7800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>17400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>31500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>7000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1700</v>
       </c>
-      <c r="V10" s="3">
-        <v>0</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="W10" s="3">
+        <v>0</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="3">
         <v>4500</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1040,8 +1050,11 @@
       <c r="AD10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1072,8 +1085,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1137,29 +1151,32 @@
       <c r="W12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X12" s="3">
+      <c r="X12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y12" s="3">
         <v>400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>200</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>300</v>
       </c>
       <c r="AA12" s="3">
         <v>300</v>
       </c>
       <c r="AB12" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AC12" s="3">
         <v>100</v>
       </c>
       <c r="AD12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE12" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1244,59 +1261,62 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="3">
         <v>2100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-500</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
         <v>2100</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>48600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>27000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>14700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>18900</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>9000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1312,8 +1332,8 @@
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1330,79 +1350,82 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E15" s="3">
         <v>8700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>9400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>9300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>100</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="3" t="s">
-        <v>4</v>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
       </c>
       <c r="AA15" s="3" t="s">
         <v>4</v>
@@ -1410,14 +1433,17 @@
       <c r="AB15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC15" s="3">
-        <v>0</v>
+      <c r="AC15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1445,180 +1471,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>77500</v>
+      </c>
+      <c r="E17" s="3">
         <v>-2700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>59500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>40500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>-16800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>18600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>70300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>19300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>26000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>26600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4700</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>1800</v>
       </c>
       <c r="AC17" s="3">
         <v>1800</v>
       </c>
       <c r="AD17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AE17" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-52600</v>
+      </c>
+      <c r="E18" s="3">
         <v>28300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-36700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-11600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>47100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-62500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-14400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-17900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-15600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>25700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-500</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-400</v>
       </c>
       <c r="AC18" s="3">
         <v>-400</v>
       </c>
       <c r="AD18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AE18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1649,65 +1682,66 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>-4000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="I20" s="3">
         <v>-2300</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>10400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>800</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -1715,17 +1749,17 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>200</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
@@ -1735,82 +1769,85 @@
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-49700</v>
+      </c>
+      <c r="E21" s="3">
         <v>41900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-28900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3200</v>
       </c>
-      <c r="G21" s="3">
-        <v>58000</v>
-      </c>
       <c r="H21" s="3">
+        <v>58400</v>
+      </c>
+      <c r="I21" s="3">
         <v>3900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-53900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-11300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-15400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>39700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-6400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-700</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>-400</v>
       </c>
       <c r="AB21" s="3">
         <v>-400</v>
@@ -1819,10 +1856,13 @@
         <v>-400</v>
       </c>
       <c r="AD21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AE21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1850,8 +1890,8 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1907,114 +1947,120 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-57000</v>
+      </c>
+      <c r="E23" s="3">
         <v>30200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-38200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-11400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>51700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-63300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-12800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-19200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>36100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-500</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>-400</v>
       </c>
       <c r="AC23" s="3">
         <v>-400</v>
       </c>
       <c r="AD23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AE23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>700</v>
+      </c>
+      <c r="E24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1600</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3">
         <v>100</v>
@@ -2023,32 +2069,32 @@
         <v>100</v>
       </c>
       <c r="L24" s="3">
+        <v>100</v>
+      </c>
+      <c r="M24" s="3">
         <v>-600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
@@ -2058,17 +2104,17 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>0</v>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>100</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>-100</v>
       </c>
       <c r="AB24" s="3">
         <v>-100</v>
@@ -2077,10 +2123,13 @@
         <v>-100</v>
       </c>
       <c r="AD24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2165,180 +2214,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-57700</v>
+      </c>
+      <c r="E26" s="3">
         <v>29000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-38800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>50100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-62700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-14500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-17800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-20100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>35800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-400</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>-300</v>
       </c>
       <c r="AC26" s="3">
         <v>-300</v>
       </c>
       <c r="AD26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AE26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-57700</v>
+      </c>
+      <c r="E27" s="3">
         <v>29000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-38800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>50100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-62700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-17800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-20100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>35800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2423,8 +2481,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2458,14 +2519,14 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>4</v>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -2477,40 +2538,43 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U29" s="3">
         <v>-100</v>
       </c>
       <c r="V29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W29" s="3">
         <v>-3700</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-7700</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA29" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2595,8 +2659,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2681,65 +2748,68 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E32" s="3">
         <v>4900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
-        <v>4000</v>
-      </c>
       <c r="H32" s="3">
+        <v>4500</v>
+      </c>
+      <c r="I32" s="3">
         <v>2300</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>6900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-10400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-800</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -2747,17 +2817,17 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>1200</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-200</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
@@ -2767,94 +2837,100 @@
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-57700</v>
+      </c>
+      <c r="E33" s="3">
         <v>29000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-38800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>50100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-62700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-14500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-17800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-20100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>35800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2200</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
       <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
         <v>-4100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-9500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2939,185 +3015,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-57700</v>
+      </c>
+      <c r="E35" s="3">
         <v>29000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-38800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>50100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-62700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-14500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-17800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-20100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>35800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2200</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
       <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
         <v>-4100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-9500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3148,8 +3233,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3180,94 +3266,98 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>57600</v>
+      </c>
+      <c r="E41" s="3">
         <v>95200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>103200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>59000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>33100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>20800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>18500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>27900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>32700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>32300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>44300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>28100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>42400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>26500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>28300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2500</v>
       </c>
-      <c r="W41" s="3">
-        <v>0</v>
-      </c>
       <c r="X41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
         <v>400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>10000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6200</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3296,41 +3386,41 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>27600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>23300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>26900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>43900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>29000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>35000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>21000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>29400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>6200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>200</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3346,34 +3436,37 @@
       <c r="AB42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
+      <c r="AC42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E43" s="3">
         <v>14100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>13900</v>
-      </c>
-      <c r="I43" s="3">
-        <v>700</v>
       </c>
       <c r="J43" s="3">
         <v>700</v>
@@ -3382,17 +3475,17 @@
         <v>700</v>
       </c>
       <c r="L43" s="3">
+        <v>700</v>
+      </c>
+      <c r="M43" s="3">
         <v>800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>200</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3408,38 +3501,41 @@
       <c r="T43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
-      <c r="V43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W43" s="3">
+      <c r="U43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X43" s="3">
         <v>500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>700</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3467,8 +3563,8 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3524,65 +3620,68 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>86500</v>
+      </c>
+      <c r="E45" s="3">
         <v>164700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>121400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>142600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>140900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>49800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>42100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>34700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>28400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>12700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>18900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2100</v>
       </c>
-      <c r="U45" s="3">
-        <v>0</v>
-      </c>
       <c r="V45" s="3">
         <v>0</v>
       </c>
@@ -3590,155 +3689,161 @@
         <v>0</v>
       </c>
       <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
         <v>100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>700</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>188000</v>
+      </c>
+      <c r="E46" s="3">
         <v>296900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>258500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>217200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>189500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>83300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>66500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>56000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>58700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>64400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>68400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>78400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>78300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>90300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>64600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>59600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>34500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>12100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>10100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>9600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7600</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E47" s="3">
         <v>30800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>28700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4000</v>
-      </c>
-      <c r="J47" s="3">
-        <v>3900</v>
       </c>
       <c r="K47" s="3">
         <v>3900</v>
       </c>
       <c r="L47" s="3">
+        <v>3900</v>
+      </c>
+      <c r="M47" s="3">
         <v>1800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2400</v>
-      </c>
-      <c r="N47" s="3">
-        <v>300</v>
       </c>
       <c r="O47" s="3">
         <v>300</v>
       </c>
       <c r="P47" s="3">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="Q47" s="3">
         <v>1000</v>
@@ -3749,8 +3854,8 @@
       <c r="S47" s="3">
         <v>1000</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>4</v>
+      <c r="T47" s="3">
+        <v>1000</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>4</v>
@@ -3767,8 +3872,8 @@
       <c r="Y47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -3782,79 +3887,82 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>200400</v>
+      </c>
+      <c r="E48" s="3">
         <v>122300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>77800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>79000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>85000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>87700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>25100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>24500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>80700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>90000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>28700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>71600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>30000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>36000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>28200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>29800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>17700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4400</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
-      </c>
       <c r="X48" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="Y48" s="3">
         <v>700</v>
       </c>
       <c r="Z48" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AA48" s="3">
         <v>100</v>
@@ -3865,20 +3973,23 @@
       <c r="AC48" s="3">
         <v>100</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E49" s="3">
         <v>32400</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
@@ -3954,8 +4065,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4040,8 +4154,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4126,94 +4243,100 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E52" s="3">
         <v>47700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>13300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>62300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>49900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>14800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>11500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>14400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1300</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V52" s="3">
+      <c r="V52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W52" s="3">
         <v>6900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1300</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4298,94 +4421,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>485200</v>
+      </c>
+      <c r="E54" s="3">
         <v>538200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>376000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>315500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>291100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>189300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>108700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>100400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>92200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>100400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>164700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>179000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>169600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>173700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>110400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>108100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>78100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>39900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>20600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>12500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>15300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>13000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9000</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4416,8 +4545,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4448,71 +4578,72 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E57" s="3">
         <v>3400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2500</v>
-      </c>
-      <c r="S57" s="3">
-        <v>1400</v>
       </c>
       <c r="T57" s="3">
         <v>1400</v>
       </c>
       <c r="U57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="V57" s="3">
         <v>300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>100</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4525,8 +4656,8 @@
       <c r="AA57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB57" s="3">
-        <v>0</v>
+      <c r="AB57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC57" s="3">
         <v>0</v>
@@ -4534,29 +4665,32 @@
       <c r="AD57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4100</v>
-      </c>
-      <c r="F58" s="3">
-        <v>2000</v>
       </c>
       <c r="G58" s="3">
         <v>2000</v>
       </c>
       <c r="H58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I58" s="3">
         <v>1900</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -4578,18 +4712,18 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
+      <c r="Q58" s="3">
+        <v>0</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T58" s="3">
         <v>1300</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4605,8 +4739,8 @@
       <c r="Y58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -4620,201 +4754,210 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E59" s="3">
         <v>47100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>41100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>400</v>
-      </c>
-      <c r="T59" s="3">
-        <v>500</v>
       </c>
       <c r="U59" s="3">
         <v>500</v>
       </c>
       <c r="V59" s="3">
+        <v>500</v>
+      </c>
+      <c r="W59" s="3">
         <v>1100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2400</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>400</v>
       </c>
       <c r="Z59" s="3">
         <v>400</v>
       </c>
       <c r="AA59" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AB59" s="3">
         <v>500</v>
       </c>
       <c r="AC59" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD59" s="3">
         <v>400</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>48300</v>
+      </c>
+      <c r="E60" s="3">
         <v>55000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>49000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>27100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2400</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>400</v>
       </c>
       <c r="Z60" s="3">
         <v>400</v>
       </c>
       <c r="AA60" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AB60" s="3">
         <v>500</v>
       </c>
       <c r="AC60" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD60" s="3">
         <v>400</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4400</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -4878,19 +5021,22 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E62" s="3">
         <v>4000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3200</v>
-      </c>
-      <c r="F62" s="3">
-        <v>5100</v>
       </c>
       <c r="G62" s="3">
         <v>5100</v>
@@ -4899,40 +5045,40 @@
         <v>5100</v>
       </c>
       <c r="I62" s="3">
-        <v>3200</v>
+        <v>5100</v>
       </c>
       <c r="J62" s="3">
         <v>3200</v>
       </c>
       <c r="K62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="L62" s="3">
         <v>3100</v>
-      </c>
-      <c r="L62" s="3">
-        <v>3000</v>
       </c>
       <c r="M62" s="3">
         <v>3000</v>
       </c>
       <c r="N62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O62" s="3">
         <v>2900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>700</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
       <c r="S62" s="3">
         <v>0</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>4</v>
+      <c r="T62" s="3">
+        <v>0</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>4</v>
@@ -4949,8 +5095,8 @@
       <c r="Y62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
+      <c r="Z62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA62" s="3">
         <v>0</v>
@@ -4964,8 +5110,11 @@
       <c r="AD62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5050,8 +5199,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5136,8 +5288,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5222,94 +5377,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>67800</v>
+      </c>
+      <c r="E66" s="3">
         <v>74800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>61000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>20200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>36600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1300</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5340,8 +5501,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5426,8 +5588,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5512,8 +5677,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5560,7 +5728,7 @@
         <v>9100</v>
       </c>
       <c r="R70" s="3">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="S70" s="3">
         <v>0</v>
@@ -5598,8 +5766,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5684,94 +5855,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-155900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-98200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-126400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-87600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-75600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-146900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-144100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-136900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-134500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-131400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-62500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-48200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-30100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-26100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-10400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>18700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>20100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-15700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-18400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-17900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-13800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-200</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5856,8 +6033,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5942,8 +6122,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6028,94 +6211,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>408400</v>
+      </c>
+      <c r="E76" s="3">
         <v>454400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>306000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>286200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>256100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>143700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>94200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>82700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>77900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>80900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>149200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>162900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>152800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>156400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>97000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>104800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>75000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>38000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>19900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7700</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6200,185 +6389,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-57700</v>
+      </c>
+      <c r="E81" s="3">
         <v>29000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-38800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>50100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-62700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-14500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-17800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-20100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>35800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2200</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
       <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3">
         <v>-4100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-9500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6409,79 +6607,80 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E83" s="3">
         <v>3400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>9400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>9300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>100</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
       <c r="X83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y83" s="3">
         <v>100</v>
       </c>
       <c r="Z83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA83" s="3">
         <v>0</v>
@@ -6495,8 +6694,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6581,8 +6783,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6667,8 +6872,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6753,8 +6961,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6839,8 +7050,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6925,94 +7139,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E89" s="3">
         <v>7300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-9500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-20900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>24300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-13900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2300</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-2500</v>
       </c>
       <c r="T89" s="3">
         <v>-2500</v>
       </c>
       <c r="U89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="V89" s="3">
         <v>-7700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-500</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
       <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7043,35 +7263,36 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-65000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-86800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-58400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -7079,44 +7300,44 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-8300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-46000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>6700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-11200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-800</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
@@ -7127,10 +7348,13 @@
         <v>0</v>
       </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7215,8 +7439,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7301,80 +7528,83 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-65000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-125000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-58400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2500</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-18300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>3800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-43700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>1800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>8600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-10700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-900</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3">
         <v>0</v>
       </c>
@@ -7385,10 +7615,13 @@
         <v>0</v>
       </c>
       <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7419,8 +7652,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7448,8 +7682,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7505,8 +7739,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7591,8 +7828,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7677,8 +7917,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7763,94 +8006,100 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E100" s="3">
         <v>111100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>51400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>41600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>38700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>30100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>16300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>21000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>71700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>28500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-8300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>6500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>13500</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z100" s="3">
         <v>5900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>5700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-400</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
         <v>0</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7878,8 +8127,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7918,107 +8167,113 @@
         <v>0</v>
       </c>
       <c r="Y101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z101" s="3">
         <v>-100</v>
       </c>
       <c r="AA101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB101" s="3">
         <v>300</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>100</v>
       </c>
       <c r="AC101" s="3">
         <v>100</v>
       </c>
       <c r="AD101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-37600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>44200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>25900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>17300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-9400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-12000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>16200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-13000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>28000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>5100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>6700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BTBT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BTBT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
   <si>
     <t>BTBT</t>
   </si>
@@ -656,298 +656,305 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E8" s="3">
         <v>24800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>25600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>22700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>29000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>30300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>16100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>28300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>44000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>20400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>700</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
-      </c>
       <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
         <v>4500</v>
       </c>
-      <c r="Z8" s="3">
-        <v>0</v>
-      </c>
       <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3">
         <v>4900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4200</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>1400</v>
       </c>
       <c r="AD8" s="3">
         <v>1400</v>
       </c>
       <c r="AE8" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AF8" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E9" s="3">
         <v>12800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>15200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>9900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>6200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>700</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="3" t="s">
-        <v>4</v>
+      <c r="Y9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>0</v>
       </c>
       <c r="AA9" s="3" t="s">
         <v>4</v>
@@ -964,80 +971,83 @@
       <c r="AE9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E10" s="3">
         <v>12000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>14100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>8600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>7800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>17400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>31500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>7000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1700</v>
       </c>
-      <c r="W10" s="3">
-        <v>0</v>
-      </c>
-      <c r="X10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y10" s="3">
+      <c r="X10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z10" s="3">
         <v>4500</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1053,8 +1063,11 @@
       <c r="AE10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1086,8 +1099,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1154,29 +1168,32 @@
       <c r="X12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Y12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z12" s="3">
         <v>400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>200</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>300</v>
       </c>
       <c r="AB12" s="3">
         <v>300</v>
       </c>
       <c r="AC12" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AD12" s="3">
         <v>100</v>
       </c>
       <c r="AE12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF12" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1264,62 +1281,65 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>2100</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>48600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>27000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>14700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>18900</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>9000</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1335,8 +1355,8 @@
       <c r="Y14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1353,82 +1373,85 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E15" s="3">
         <v>7200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>9400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>9300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>100</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="3" t="s">
-        <v>4</v>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>4</v>
@@ -1436,14 +1459,17 @@
       <c r="AC15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD15" s="3">
-        <v>0</v>
+      <c r="AD15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1472,186 +1498,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E17" s="3">
         <v>77500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>-2700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>59500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>40500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>-16800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>70300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>23500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>24700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>19300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>26000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>26600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>18900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4700</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>1800</v>
       </c>
       <c r="AD17" s="3">
         <v>1800</v>
       </c>
       <c r="AE17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AF17" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-52600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>28300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-36700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-11600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>47100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-62500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-14400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-17900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-15600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>25700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-500</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-400</v>
       </c>
       <c r="AD18" s="3">
         <v>-400</v>
       </c>
       <c r="AE18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AF18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1683,68 +1716,69 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E20" s="3">
         <v>4300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2300</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-6900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>10400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>800</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1752,17 +1786,17 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>200</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
@@ -1772,85 +1806,88 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-49700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>41900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-28900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>58400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-3400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-53900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-11300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-9500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-15400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>39700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-700</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>-400</v>
       </c>
       <c r="AC21" s="3">
         <v>-400</v>
@@ -1859,10 +1896,13 @@
         <v>-400</v>
       </c>
       <c r="AE21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AF21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1893,8 +1933,8 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1950,120 +1990,126 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-57000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>30200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-38200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-11400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>51700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-63300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-14300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-16600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-12800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-19200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>36100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-500</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>-400</v>
       </c>
       <c r="AD23" s="3">
         <v>-400</v>
       </c>
       <c r="AE23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AF23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E24" s="3">
         <v>700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1600</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3">
         <v>100</v>
@@ -2072,32 +2118,32 @@
         <v>100</v>
       </c>
       <c r="M24" s="3">
+        <v>100</v>
+      </c>
+      <c r="N24" s="3">
         <v>-600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
@@ -2107,17 +2153,17 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>0</v>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>100</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>-100</v>
       </c>
       <c r="AC24" s="3">
         <v>-100</v>
@@ -2126,10 +2172,13 @@
         <v>-100</v>
       </c>
       <c r="AE24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2217,186 +2266,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-57700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>29000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-38800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-12000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>50100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-62700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-14500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-17800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-15300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-20100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>35800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-400</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>-300</v>
       </c>
       <c r="AD26" s="3">
         <v>-300</v>
       </c>
       <c r="AE26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AF26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-57700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>29000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-38800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-12000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>50100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-62700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-14500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-17800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-15300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-20100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>35800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2484,8 +2542,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2522,14 +2583,14 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>4</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2541,40 +2602,43 @@
         <v>0</v>
       </c>
       <c r="U29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V29" s="3">
         <v>-100</v>
       </c>
       <c r="W29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X29" s="3">
         <v>-3700</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB29" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
+      <c r="AD29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2662,8 +2726,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2751,68 +2818,71 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2300</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>6900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-10400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-800</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -2820,17 +2890,17 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>1200</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-200</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
@@ -2840,97 +2910,103 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-57700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>29000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-38800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-12000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>50100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-62700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-14500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-17800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-15300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-20100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>35800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2200</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
       <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
         <v>-4100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-9500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3018,191 +3094,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-57700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>29000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-38800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-12000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>50100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-62700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-14500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-17800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-15300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-20100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>35800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2200</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
       <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
         <v>-4100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-9500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3234,8 +3319,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3267,97 +3353,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>181200</v>
+      </c>
+      <c r="E41" s="3">
         <v>57600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>95200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>103200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>59000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>33100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>20800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>18500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>27900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>32700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>32300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>44300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>28100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>42400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>26500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>28300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2500</v>
       </c>
-      <c r="X41" s="3">
-        <v>0</v>
-      </c>
       <c r="Y41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="3">
         <v>400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>10000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6200</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3389,41 +3479,41 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>27600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>23300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>26900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>43900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>29000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>35000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>21000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>29400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>6200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>200</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3439,37 +3529,40 @@
       <c r="AC42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD42" s="3">
-        <v>0</v>
+      <c r="AD42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E43" s="3">
         <v>23500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>14100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>13500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>13900</v>
-      </c>
-      <c r="J43" s="3">
-        <v>700</v>
       </c>
       <c r="K43" s="3">
         <v>700</v>
@@ -3478,17 +3571,17 @@
         <v>700</v>
       </c>
       <c r="M43" s="3">
+        <v>700</v>
+      </c>
+      <c r="N43" s="3">
         <v>800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>200</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3504,38 +3597,41 @@
       <c r="U43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
-      <c r="W43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X43" s="3">
+      <c r="V43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y43" s="3">
         <v>500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>700</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3566,8 +3662,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3623,68 +3719,71 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>99500</v>
+      </c>
+      <c r="E45" s="3">
         <v>86500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>164700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>121400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>142600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>140900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>49800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>42100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>34700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>28400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>18900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2100</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
-      </c>
       <c r="W45" s="3">
         <v>0</v>
       </c>
@@ -3692,161 +3791,167 @@
         <v>0</v>
       </c>
       <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3">
         <v>100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>4300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>700</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>313800</v>
+      </c>
+      <c r="E46" s="3">
         <v>188000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>296900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>258500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>217200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>189500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>83300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>66500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>56000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>58700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>64400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>68400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>78400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>78300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>90300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>64600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>59600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>34500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>12100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>10100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>9600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7600</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E47" s="3">
         <v>33100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>30800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>28700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4000</v>
-      </c>
-      <c r="K47" s="3">
-        <v>3900</v>
       </c>
       <c r="L47" s="3">
         <v>3900</v>
       </c>
       <c r="M47" s="3">
+        <v>3900</v>
+      </c>
+      <c r="N47" s="3">
         <v>1800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2400</v>
-      </c>
-      <c r="O47" s="3">
-        <v>300</v>
       </c>
       <c r="P47" s="3">
         <v>300</v>
       </c>
       <c r="Q47" s="3">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="R47" s="3">
         <v>1000</v>
@@ -3857,8 +3962,8 @@
       <c r="T47" s="3">
         <v>1000</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>4</v>
+      <c r="U47" s="3">
+        <v>1000</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>4</v>
@@ -3875,8 +3980,8 @@
       <c r="Z47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
+      <c r="AA47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB47" s="3">
         <v>0</v>
@@ -3890,82 +3995,85 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>298700</v>
+      </c>
+      <c r="E48" s="3">
         <v>200400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>122300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>77800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>79000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>85000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>87700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>25100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>24500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>19000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>80700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>90000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>28700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>71600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>30000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>36000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>28200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>29800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>17700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4400</v>
       </c>
-      <c r="X48" s="3">
-        <v>0</v>
-      </c>
       <c r="Y48" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="Z48" s="3">
         <v>700</v>
       </c>
       <c r="AA48" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AB48" s="3">
         <v>100</v>
@@ -3976,23 +4084,26 @@
       <c r="AD48" s="3">
         <v>100</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E49" s="3">
         <v>32000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>32400</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
@@ -4068,8 +4179,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4157,8 +4271,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4246,97 +4363,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E52" s="3">
         <v>23600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>47700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>13300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>62300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>49900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>14800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>14400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1300</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W52" s="3">
+      <c r="W52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X52" s="3">
         <v>6900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1300</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4424,97 +4547,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>723400</v>
+      </c>
+      <c r="E54" s="3">
         <v>485200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>538200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>376000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>315500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>291100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>189300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>108700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>100400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>92200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>100400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>164700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>179000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>169600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>173700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>110400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>108100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>78100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>39900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>20600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>14000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>12500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>15300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>13000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>9000</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4546,8 +4675,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4579,74 +4709,75 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2500</v>
-      </c>
-      <c r="T57" s="3">
-        <v>1400</v>
       </c>
       <c r="U57" s="3">
         <v>1400</v>
       </c>
       <c r="V57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W57" s="3">
         <v>300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>100</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4659,8 +4790,8 @@
       <c r="AB57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC57" s="3">
-        <v>0</v>
+      <c r="AC57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD57" s="3">
         <v>0</v>
@@ -4668,32 +4799,35 @@
       <c r="AE57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E58" s="3">
         <v>5000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4100</v>
-      </c>
-      <c r="G58" s="3">
-        <v>2000</v>
       </c>
       <c r="H58" s="3">
         <v>2000</v>
       </c>
       <c r="I58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J58" s="3">
         <v>1900</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -4715,18 +4849,18 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>4</v>
+      <c r="R58" s="3">
+        <v>0</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U58" s="3">
         <v>1300</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4742,8 +4876,8 @@
       <c r="Z58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
@@ -4757,210 +4891,219 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E59" s="3">
         <v>41400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>47100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>41100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>22900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>400</v>
-      </c>
-      <c r="U59" s="3">
-        <v>500</v>
       </c>
       <c r="V59" s="3">
         <v>500</v>
       </c>
       <c r="W59" s="3">
+        <v>500</v>
+      </c>
+      <c r="X59" s="3">
         <v>1100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2400</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>400</v>
       </c>
       <c r="AA59" s="3">
         <v>400</v>
       </c>
       <c r="AB59" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AC59" s="3">
         <v>500</v>
       </c>
       <c r="AD59" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE59" s="3">
         <v>400</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E60" s="3">
         <v>48300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>55000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>49000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>27100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2400</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>400</v>
       </c>
       <c r="AA60" s="3">
         <v>400</v>
       </c>
       <c r="AB60" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AC60" s="3">
         <v>500</v>
       </c>
       <c r="AD60" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE60" s="3">
         <v>400</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E61" s="3">
         <v>9000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4400</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -5024,22 +5167,25 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E62" s="3">
         <v>3800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3200</v>
-      </c>
-      <c r="G62" s="3">
-        <v>5100</v>
       </c>
       <c r="H62" s="3">
         <v>5100</v>
@@ -5048,40 +5194,40 @@
         <v>5100</v>
       </c>
       <c r="J62" s="3">
-        <v>3200</v>
+        <v>5100</v>
       </c>
       <c r="K62" s="3">
         <v>3200</v>
       </c>
       <c r="L62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="M62" s="3">
         <v>3100</v>
-      </c>
-      <c r="M62" s="3">
-        <v>3000</v>
       </c>
       <c r="N62" s="3">
         <v>3000</v>
       </c>
       <c r="O62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="P62" s="3">
         <v>2900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>700</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
-      </c>
       <c r="T62" s="3">
         <v>0</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>4</v>
+      <c r="U62" s="3">
+        <v>0</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>4</v>
@@ -5098,8 +5244,8 @@
       <c r="Z62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB62" s="3">
         <v>0</v>
@@ -5113,8 +5259,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5202,8 +5351,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5291,8 +5443,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5380,97 +5535,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>90200</v>
+      </c>
+      <c r="E66" s="3">
         <v>67800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>74800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>61000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>20200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>25900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>36600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1300</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5502,8 +5663,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5591,8 +5753,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5680,8 +5845,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5731,7 +5899,7 @@
         <v>9100</v>
       </c>
       <c r="S70" s="3">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="T70" s="3">
         <v>0</v>
@@ -5769,8 +5937,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5858,97 +6029,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-141000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-155900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-98200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-126400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-87600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-75600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-146900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-144100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-136900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-134500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-131400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-62500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-48200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-30100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-26100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-10400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>18700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>20100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-15700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-18400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-17900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-13800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-10800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-200</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6036,8 +6213,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6125,8 +6305,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6214,97 +6397,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>624100</v>
+      </c>
+      <c r="E76" s="3">
         <v>408400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>454400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>306000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>286200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>256100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>143700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>94200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>82700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>77900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>80900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>149200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>162900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>152800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>156400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>97000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>104800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>75000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>38000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>19900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>11600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7700</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6392,191 +6581,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-57700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>29000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-38800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-12000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>50100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-62700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-14500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-17800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-15300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-20100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>35800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2200</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
       <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
         <v>-4100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-9500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6608,82 +6806,83 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E83" s="3">
         <v>7200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>9400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>9300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>100</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
-      </c>
       <c r="Y83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z83" s="3">
         <v>100</v>
       </c>
       <c r="AA83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
@@ -6697,8 +6896,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6786,8 +6988,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6875,8 +7080,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6964,8 +7172,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7053,8 +7264,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7142,97 +7356,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E89" s="3">
         <v>17400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-20900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>24300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-13900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-9700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2300</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-2500</v>
       </c>
       <c r="U89" s="3">
         <v>-2500</v>
       </c>
       <c r="V89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="W89" s="3">
         <v>-7700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-500</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
-      </c>
       <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7264,38 +7484,39 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-82200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-65000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-86800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-58400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -7303,44 +7524,44 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-8300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-46000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>6700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-11200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-800</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
       <c r="AB91" s="3">
         <v>0</v>
       </c>
@@ -7351,10 +7572,13 @@
         <v>0</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7442,8 +7666,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7531,83 +7758,86 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-83300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-65000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-125000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-17300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-58400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2500</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-18300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>3800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-43700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>1100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>8600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-10700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-900</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="Z94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
         <v>0</v>
       </c>
@@ -7618,10 +7848,13 @@
         <v>0</v>
       </c>
       <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7653,8 +7886,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7685,8 +7919,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7742,8 +7976,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7831,8 +8068,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7920,8 +8160,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8009,97 +8252,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>189900</v>
+      </c>
+      <c r="E100" s="3">
         <v>9400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>111100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>51400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>41600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>38700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>30100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>16300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>21000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>71700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>28500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-8300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>6500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>13500</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA100" s="3">
         <v>5900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>5700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-400</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
         <v>0</v>
       </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8130,8 +8379,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -8170,110 +8419,116 @@
         <v>0</v>
       </c>
       <c r="Z101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA101" s="3">
         <v>-100</v>
       </c>
       <c r="AB101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC101" s="3">
         <v>300</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>100</v>
       </c>
       <c r="AD101" s="3">
         <v>100</v>
       </c>
       <c r="AE101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>123600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-37600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>44200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>25900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>17300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>16200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>28000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>6700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BTBT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BTBT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
   <si>
     <t>BTBT</t>
   </si>
@@ -656,241 +656,254 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>31900</v>
+      </c>
+      <c r="F8" s="3">
         <v>30000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>25300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>24800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>25600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>22700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>29000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>30300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>16100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>11600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>9000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>8300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>7800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>9100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>6800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>8600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>13400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>10400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>28300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>44000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>20400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>7900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>700</v>
       </c>
-      <c r="Z8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
         <v>4500</v>
       </c>
-      <c r="AB8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3">
         <v>4900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>4200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>1400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>1400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -898,79 +911,79 @@
         <v>12100</v>
       </c>
       <c r="E9" s="3">
+        <v>14300</v>
+      </c>
+      <c r="F9" s="3">
+        <v>12100</v>
+      </c>
+      <c r="G9" s="3">
         <v>13200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>12800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>15600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>15500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>15200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>16200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>9900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>8800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>5700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>5200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>6000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>6500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>3600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>4300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>4800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>2600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>10900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>12500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>13400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>6200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>700</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>0</v>
-      </c>
       <c r="AB9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>4</v>
+      <c r="AC9" s="3">
+        <v>0</v>
       </c>
       <c r="AD9" s="3" t="s">
         <v>4</v>
@@ -984,89 +997,95 @@
       <c r="AG9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>17600</v>
+      </c>
+      <c r="F10" s="3">
         <v>17900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>12100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>12000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>10000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>7200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>13800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>14100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>6100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>2800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>3400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>3100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>2600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>3200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>4300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>8600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>7800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>17400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>31500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>7000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1700</v>
       </c>
-      <c r="Y10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC10" s="3">
         <v>4500</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1079,8 +1098,14 @@
       <c r="AG10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1114,8 +1139,10 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1188,29 +1215,35 @@
       <c r="Z12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AA12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC12" s="3">
         <v>400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1304,71 +1337,77 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E14" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F14" s="3">
         <v>500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>2100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="3">
-        <v>2100</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>48600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>2700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>27000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>14700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>18900</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>9000</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1381,11 +1420,11 @@
       <c r="AA14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1399,103 +1438,115 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>11700</v>
+      </c>
+      <c r="F15" s="3">
         <v>9600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>8200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>7200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>8700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>8400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>8300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>6800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>3400</v>
-      </c>
-      <c r="L15" s="3">
-        <v>3600</v>
-      </c>
-      <c r="M15" s="3">
-        <v>3700</v>
       </c>
       <c r="N15" s="3">
         <v>3600</v>
       </c>
       <c r="O15" s="3">
+        <v>3700</v>
+      </c>
+      <c r="P15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Q15" s="3">
         <v>9400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>9300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>5300</v>
-      </c>
-      <c r="R15" s="3">
-        <v>3800</v>
-      </c>
-      <c r="S15" s="3">
-        <v>3300</v>
       </c>
       <c r="T15" s="3">
         <v>3800</v>
       </c>
       <c r="U15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="V15" s="3">
+        <v>3800</v>
+      </c>
+      <c r="W15" s="3">
         <v>2300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>3700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>3300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>1200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>100</v>
       </c>
-      <c r="Z15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB15" s="3">
         <v>0</v>
       </c>
       <c r="AC15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>4</v>
+      <c r="AD15" s="3">
+        <v>0</v>
       </c>
       <c r="AE15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1526,198 +1577,212 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>170800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>225300</v>
+      </c>
+      <c r="F17" s="3">
         <v>-111300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>13900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>77500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>-2700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>59500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>40500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>-16800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>17900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>18600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>11700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>14000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>70300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>23500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>24700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>14900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>19300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>26000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>26600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>18300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>18900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>7800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>9800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>5700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>4700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>1800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>1800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-143300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-193400</v>
+      </c>
+      <c r="F18" s="3">
         <v>141300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>11400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-52600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>28300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-36700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-11600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>47100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-1900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-7000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-2600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-5700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-62500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-14400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-17900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-6300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-5900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-15600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>1700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>25700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-5300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1751,206 +1816,220 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-6200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-4700</v>
       </c>
-      <c r="F20" s="3">
-        <v>4300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-4900</v>
-      </c>
       <c r="H20" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J20" s="3">
         <v>1600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-4500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-2300</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-3400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>1300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-6900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-3700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-2900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>10400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>800</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-137700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-174700</v>
+      </c>
+      <c r="F21" s="3">
         <v>157100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>24400</v>
       </c>
-      <c r="F21" s="3">
-        <v>-49700</v>
-      </c>
-      <c r="G21" s="3">
-        <v>41900</v>
-      </c>
       <c r="H21" s="3">
+        <v>-50300</v>
+      </c>
+      <c r="I21" s="3">
+        <v>35700</v>
+      </c>
+      <c r="J21" s="3">
         <v>-29900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-3200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>58400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>3900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-3400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-53900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-11300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-1900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-9500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-15400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>1100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>39700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>5500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>1300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-700</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AE21" s="3">
-        <v>-400</v>
       </c>
       <c r="AF21" s="3">
         <v>-400</v>
       </c>
       <c r="AG21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AH21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AI21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>4</v>
+      <c r="D22" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E22" s="3">
+        <v>3100</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>4</v>
@@ -1979,11 +2058,11 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2036,198 +2115,216 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-149900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-193800</v>
+      </c>
+      <c r="F23" s="3">
         <v>147400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>16500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-57000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>30200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-38200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-11400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>51700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-2000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-7100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-2200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-63300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-16600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-5700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-12800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-19200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-1200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>36100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>2300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="E24" s="3">
-        <v>1600</v>
+        <v>-5000</v>
       </c>
       <c r="F24" s="3">
         <v>700</v>
       </c>
       <c r="G24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H24" s="3">
+        <v>700</v>
+      </c>
+      <c r="I24" s="3">
         <v>1200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1600</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>100</v>
-      </c>
       <c r="M24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N24" s="3">
         <v>100</v>
       </c>
       <c r="O24" s="3">
+        <v>100</v>
+      </c>
+      <c r="P24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>1200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-1400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>2500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>4</v>
+      <c r="AA24" s="3">
+        <v>0</v>
       </c>
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AC24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>100</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>-100</v>
       </c>
       <c r="AF24" s="3">
         <v>-100</v>
       </c>
       <c r="AG24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2321,198 +2418,216 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-150300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-188800</v>
+      </c>
+      <c r="F26" s="3">
         <v>146700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>14900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-57700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>29000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-38800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-12000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>50100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-2000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-7200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-2300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-62700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-17800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-4300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-15300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-20100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-1300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>35800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>2300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-146700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-188400</v>
+      </c>
+      <c r="F27" s="3">
         <v>150900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>14900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-57700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>29000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-38800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-12000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>50100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-2000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-7200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-2300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-62700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-17800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-4300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-15300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-20100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-1300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>35800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>2300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-400</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>-6500</v>
       </c>
       <c r="AB27" s="3">
         <v>-1800</v>
       </c>
       <c r="AC27" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2606,8 +2721,14 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2650,17 +2771,17 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -2669,40 +2790,46 @@
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-100</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>-100</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="AA29" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2796,8 +2923,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2891,198 +3024,216 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F32" s="3">
         <v>6200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>4700</v>
       </c>
-      <c r="F32" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>4900</v>
-      </c>
       <c r="H32" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J32" s="3">
         <v>-1600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>4500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>2300</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>3400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-1300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>6900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>3700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>2900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-10400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-800</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>1200</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-146700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-188400</v>
+      </c>
+      <c r="F33" s="3">
         <v>150900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>14900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-57700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>29000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-38800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-12000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>50100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-2000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-7200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-2300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-62700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-17800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-4300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-15300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-20100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-1300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>35800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>2200</v>
       </c>
-      <c r="X33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-9500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3176,203 +3327,221 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-146700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-188400</v>
+      </c>
+      <c r="F35" s="3">
         <v>150900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>14900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-57700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>29000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-38800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-12000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>50100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-2000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-7200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-2300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-62700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-17800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-4300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-15300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-20100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-1300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>35800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>2200</v>
       </c>
-      <c r="X35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-9500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3406,8 +3575,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3441,103 +3612,111 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>79500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>118400</v>
+      </c>
+      <c r="F41" s="3">
         <v>179100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>181200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>57600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>95200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>103200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>59000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>33100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>16900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>20800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>18500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>27900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>32700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>32300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>44300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>28100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>42400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>26500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>28300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>2500</v>
       </c>
-      <c r="Z41" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="3">
         <v>400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>2300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>10000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>5500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>5600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>6200</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3575,44 +3754,44 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>27600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>23300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>26900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>43900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>29000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>35000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>21000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>29400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>6200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>200</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3625,65 +3804,71 @@
       <c r="AE42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>100400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>34000</v>
+      </c>
+      <c r="F43" s="3">
         <v>30000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>17000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>23500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>14100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>13500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>11300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>11200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>13900</v>
-      </c>
-      <c r="L43" s="3">
-        <v>700</v>
-      </c>
-      <c r="M43" s="3">
-        <v>700</v>
       </c>
       <c r="N43" s="3">
         <v>700</v>
       </c>
       <c r="O43" s="3">
+        <v>700</v>
+      </c>
+      <c r="P43" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q43" s="3">
         <v>800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>200</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3696,38 +3881,44 @@
       <c r="W43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="X43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB43" s="3">
         <v>500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>1000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>700</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3764,11 +3955,11 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3821,251 +4012,269 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>305400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>427000</v>
+      </c>
+      <c r="F45" s="3">
         <v>447600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>99500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>86500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>164700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>121400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>142600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>140900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>49800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>42100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>34700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>28400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>3400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>12700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>7000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>6300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>18900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>3100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>10400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>4900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>2100</v>
       </c>
-      <c r="X45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>0</v>
-      </c>
       <c r="Z45" s="3">
         <v>0</v>
       </c>
       <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="3">
         <v>100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>3200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>4300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>3900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>700</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>499700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>593700</v>
+      </c>
+      <c r="F46" s="3">
         <v>672700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>313800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>188000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>296900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>258500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>217200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>189500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>83300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>66500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>56000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>58700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>64400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>68400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>78400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>78300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>90300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>64600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>59600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>34500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>8700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>3000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>2700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>5700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>12100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>10100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>9600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>7600</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>69100</v>
+      </c>
+      <c r="F47" s="3">
         <v>86700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>39000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>33100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>30800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>28700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>6000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>4800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>4400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>4000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>3900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>3900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>2400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>300</v>
-      </c>
-      <c r="S47" s="3">
-        <v>1000</v>
-      </c>
-      <c r="T47" s="3">
-        <v>1000</v>
       </c>
       <c r="U47" s="3">
         <v>1000</v>
@@ -4073,11 +4282,11 @@
       <c r="V47" s="3">
         <v>1000</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X47" s="3" t="s">
-        <v>4</v>
+      <c r="W47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X47" s="3">
+        <v>1000</v>
       </c>
       <c r="Y47" s="3" t="s">
         <v>4</v>
@@ -4091,11 +4300,11 @@
       <c r="AB47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD47" s="3">
-        <v>0</v>
+      <c r="AC47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE47" s="3">
         <v>0</v>
@@ -4106,91 +4315,97 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>482800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>384900</v>
+      </c>
+      <c r="F48" s="3">
         <v>314100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>298700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>200400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>122300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>77800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>79000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>85000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>87700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>25100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>24500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>19000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>22600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>80700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>90000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>28700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>71600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>30000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>36000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>28200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>29800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>17700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>4400</v>
       </c>
-      <c r="Z48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="3">
         <v>700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>700</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>100</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>100</v>
       </c>
       <c r="AE48" s="3">
         <v>100</v>
@@ -4198,32 +4413,38 @@
       <c r="AF48" s="3">
         <v>100</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>33000</v>
+      </c>
+      <c r="F49" s="3">
         <v>32700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>33400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>32000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>32400</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
@@ -4296,8 +4517,14 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4391,8 +4618,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4486,103 +4719,115 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>58400</v>
+      </c>
+      <c r="F52" s="3">
         <v>15500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>28100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>23600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>47700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>7000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>9400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>7300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>11600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>12800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>14400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>10200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>11600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>13300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>10200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>62300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>49900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>14800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>11500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>14400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>1300</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA52" s="3">
         <v>6900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>4000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>5400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>6100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>3100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>2800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>3300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>1300</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4676,103 +4921,115 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1180700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1174400</v>
+      </c>
+      <c r="F54" s="3">
         <v>1133100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>723400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>485200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>538200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>376000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>315500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>291100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>189300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>108700</v>
-      </c>
-      <c r="M54" s="3">
-        <v>100400</v>
-      </c>
-      <c r="N54" s="3">
-        <v>92200</v>
       </c>
       <c r="O54" s="3">
         <v>100400</v>
       </c>
       <c r="P54" s="3">
+        <v>92200</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>100400</v>
+      </c>
+      <c r="R54" s="3">
         <v>164700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>179000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>169600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>173700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>110400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>108100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>78100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>39900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>20600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>14000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>4500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>7500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>12500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>15300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>12900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>13000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>9000</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4806,8 +5063,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4841,83 +5100,85 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F57" s="3">
         <v>6300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>3700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>5600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>3600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>3500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>2600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>3000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>100</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4927,50 +5188,56 @@
       <c r="AD57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF57" s="3">
-        <v>0</v>
+      <c r="AE57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>18500</v>
+      </c>
+      <c r="F58" s="3">
         <v>5600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>5500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>5000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>4500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>4100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1900</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4989,21 +5256,21 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V58" s="3">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X58" s="3">
         <v>1300</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5016,11 +5283,11 @@
       <c r="AB58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>0</v>
+      <c r="AC58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE58" s="3">
         <v>0</v>
@@ -5031,231 +5298,249 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>51900</v>
+      </c>
+      <c r="F59" s="3">
         <v>26400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>32500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>41400</v>
       </c>
-      <c r="G59" s="3">
-        <v>47100</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>45500</v>
+      </c>
+      <c r="J59" s="3">
         <v>41100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>5100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>7800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>22900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>4000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3800</v>
-      </c>
-      <c r="P59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>2200</v>
       </c>
       <c r="R59" s="3">
         <v>1300</v>
       </c>
       <c r="S59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="T59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="U59" s="3">
         <v>2400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1100</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>400</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>2400</v>
       </c>
       <c r="AB59" s="3">
         <v>400</v>
       </c>
       <c r="AC59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AD59" s="3">
         <v>400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF59" s="3">
         <v>500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>400</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>78500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>92900</v>
+      </c>
+      <c r="F60" s="3">
         <v>38400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>40100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>48300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>55000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>49000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>10300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>15400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>27100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>5400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>7500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>3500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>4100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>4900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>5000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>3700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>3200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>3100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1200</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>400</v>
-      </c>
-      <c r="AA60" s="3">
-        <v>2400</v>
       </c>
       <c r="AB60" s="3">
         <v>400</v>
       </c>
       <c r="AC60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AD60" s="3">
         <v>400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF60" s="3">
         <v>500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>400</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>345500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>115700</v>
+      </c>
+      <c r="F61" s="3">
         <v>36300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>38300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>9000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>9300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>7200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>3300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>3800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>4400</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -5316,73 +5601,79 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>22500</v>
+      </c>
+      <c r="F62" s="3">
         <v>3400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>3600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>3800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>4000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>3200</v>
-      </c>
-      <c r="I62" s="3">
-        <v>5100</v>
-      </c>
-      <c r="J62" s="3">
-        <v>5100</v>
       </c>
       <c r="K62" s="3">
         <v>5100</v>
       </c>
       <c r="L62" s="3">
+        <v>5100</v>
+      </c>
+      <c r="M62" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N62" s="3">
         <v>3200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>3200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>3100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>3000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>3000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>2900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>3200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>700</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
-      </c>
-      <c r="V62" s="3">
-        <v>0</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>4</v>
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
+        <v>0</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>4</v>
@@ -5396,11 +5687,11 @@
       <c r="AB62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>0</v>
+      <c r="AC62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE62" s="3">
         <v>0</v>
@@ -5411,8 +5702,14 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5506,8 +5803,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5601,8 +5904,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5696,103 +6005,115 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>572000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>309200</v>
+      </c>
+      <c r="F66" s="3">
         <v>87500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>90200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>67800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>74800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>61000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>20200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>25900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>36600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>5400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>8600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>5200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>10500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>6400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>7000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>7700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>8300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>4400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>3200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>3100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>2400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>1500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>1300</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5826,8 +6147,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5921,8 +6244,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6016,8 +6345,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6073,10 +6408,10 @@
         <v>9100</v>
       </c>
       <c r="U70" s="3">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="V70" s="3">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="W70" s="3">
         <v>0</v>
@@ -6111,8 +6446,14 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6206,103 +6547,115 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-326000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-178500</v>
+      </c>
+      <c r="F72" s="3">
         <v>9800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-141000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-155900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-98200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-126400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-87600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-75600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-146900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-144100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-136900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-134500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-131400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-62500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-48200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-30100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-26100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-10400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>18700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>20100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-15700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-18400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-17900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-13800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-200</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6396,8 +6749,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6491,8 +6850,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6586,103 +6951,115 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>460200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>714900</v>
+      </c>
+      <c r="F76" s="3">
         <v>897100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>624100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>408400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>454400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>306000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>286200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>256100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>143700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>94200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>82700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>77900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>80900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>149200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>162900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>152800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>156400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>97000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>104800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>75000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>38000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>19900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>12500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>3800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>5200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>11600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>14300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>11800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>11600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>7700</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6776,203 +7153,221 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-146700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-188400</v>
+      </c>
+      <c r="F81" s="3">
         <v>150900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>14900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-57700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>29000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-38800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-12000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>50100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-2000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-7200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-2300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-62700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-17800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-4300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-15300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-20100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-1300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>35800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>2200</v>
       </c>
-      <c r="X81" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-9500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7006,91 +7401,93 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F83" s="3">
         <v>10100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>7900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>7200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>3400</v>
-      </c>
-      <c r="H83" s="3">
-        <v>3600</v>
-      </c>
-      <c r="I83" s="3">
-        <v>3700</v>
       </c>
       <c r="J83" s="3">
         <v>3600</v>
       </c>
       <c r="K83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="L83" s="3">
+        <v>3600</v>
+      </c>
+      <c r="M83" s="3">
         <v>9400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>9300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>5300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>3800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>9400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>9300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>5300</v>
-      </c>
-      <c r="R83" s="3">
-        <v>3800</v>
-      </c>
-      <c r="S83" s="3">
-        <v>3300</v>
       </c>
       <c r="T83" s="3">
         <v>3800</v>
       </c>
       <c r="U83" s="3">
+        <v>3300</v>
+      </c>
+      <c r="V83" s="3">
+        <v>3800</v>
+      </c>
+      <c r="W83" s="3">
         <v>2300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>3700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>3300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>1200</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>0</v>
       </c>
       <c r="AA83" s="3">
         <v>100</v>
       </c>
       <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
         <v>100</v>
       </c>
-      <c r="AC83" s="3">
-        <v>0</v>
-      </c>
       <c r="AD83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE83" s="3">
         <v>0</v>
@@ -7101,8 +7498,14 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7196,8 +7599,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7291,8 +7700,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7386,8 +7801,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7481,8 +7902,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7576,103 +8003,115 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-84100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-240000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>17700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>17400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>7300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>10100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-9500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-20900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>24300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-13900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-7800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-1500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-9700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-2800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-2300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-2500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-2500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-500</v>
       </c>
-      <c r="AD89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7706,92 +8145,94 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-169200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-121900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-16900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-82200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-65000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-86800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-5100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-58400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-7100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-8300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-11100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-46000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>6700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-11200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-800</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
       <c r="AE91" s="3">
         <v>0</v>
       </c>
@@ -7799,10 +8240,16 @@
         <v>0</v>
       </c>
       <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7896,8 +8343,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7991,92 +8444,98 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-142700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-123400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-15800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-83300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-65000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-125000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-17300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-6200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-58400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-8200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-2500</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>3800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-4100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-43700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>1800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>1100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>8600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-10700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-900</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
       <c r="AE94" s="3">
         <v>0</v>
       </c>
@@ -8084,10 +8543,16 @@
         <v>0</v>
       </c>
       <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8121,8 +8586,10 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8159,11 +8626,11 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -8216,8 +8683,14 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8311,8 +8784,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8406,8 +8885,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8501,111 +8986,123 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>105100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>146400</v>
+      </c>
+      <c r="F100" s="3">
         <v>253400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>189900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>9400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>111100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>51400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>41600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>38700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>30100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>16300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>6700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>21000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-2200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>71700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>4700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>28500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>1300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-8300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>6500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>13500</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD100" s="3">
         <v>5900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>5700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-400</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>4</v>
+      <c r="D101" s="3">
+        <v>500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-100</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>4</v>
@@ -8634,11 +9131,11 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8674,116 +9171,128 @@
         <v>0</v>
       </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-38400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-60600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>123600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-37600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-6700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>44200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>25900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>17300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-3900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>2300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-9400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-4800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>16200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-13000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>15900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-1800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>28000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-2100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>1900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>5100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>6700</v>
       </c>
     </row>
